--- a/data/grammar_items/review_batch_v0_2.xlsx
+++ b/data/grammar_items/review_batch_v0_2.xlsx
@@ -724,18 +724,18 @@
       <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_697420fb30f3</t>
+          <t>gi_v02_43efa9c2d189</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -745,26 +745,26 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Between 1906 and 1908 he had taken part in a highly publicized and extremely dangerous expedition to the coast of northeast Greenland.</t>
+          <t>That is enough rock to explain the continental crust.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Between 1906 and 1908 he 【had taken】 part in a highly publicized and extremely dangerous expedition to the coast of northeast Greenland.</t>
+          <t>That 【is】 enough rock to explain the continental crust.</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="5" t="inlineStr"/>
     </row>
-    <row r="4" ht="44" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_9bdf70e3c949</t>
+          <t>gi_v02_274d00278c0e</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -779,31 +779,31 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>But the behaviour that procrastination was most closely linked with was using fraudulent excuses to get deadline extensions.</t>
+          <t>A sustainable tour is significant for ecotourism, one in which we can grow hand in hand with nature and our community, respecting everything that makes us privileged.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>But the behaviour that procrastination was most closely linked with was 【using】 fraudulent excuses to get deadline extensions.</t>
+          <t>A sustainable tour 【is】 significant for ecotourism, one in which we can grow hand in hand with nature and our community, respecting everything that makes us privileged.</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_22764934c8fe</t>
+          <t>gi_v02_9d4dad62904c</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -813,13 +813,13 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Those include inactivating satellites at the end of their useful life by venting pressurised materials or leftover fuel that might lead to explosions.</t>
+          <t>In the west at least, most food is now far cheaper to buy in relative terms than it was in 1960.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Those 【include】 inactivating satellites at the end of their useful life by venting pressurised materials or leftover fuel that might lead to explosions.</t>
+          <t>In the west at least, most food 【is】 now far cheaper to buy in relative terms than it was in 1960.</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_85c01203712f</t>
+          <t>gi_v02_552179ef0fa9</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -881,26 +881,26 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>The system will scan both Horvitz's and the caller's calendar to check if it can reschedule a callback at a time which works for both of them.</t>
+          <t>For one, the results depend in part on population-size estimates for the extinct animals – figures that are not necessarily reliable.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>The system 【will scan】 both Horvitz's and the caller's calendar to check if it can reschedule a callback at a time which works for both of them.</t>
+          <t>For one, the results 【depend】 in part on population-size estimates for the extinct animals – figures that are not necessarily reliable.</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_84143ed838eb</t>
+          <t>gi_v02_ab31cf42e1d6</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -915,13 +915,13 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Years later, after his restoration as king, the 50-year-old Charles II requested a meeting with the writer and diarist Samuel Pepys.</t>
+          <t>For the next nine years, the penniless and defeated Charles wandered around Europe with only a small group of loyal supporters.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Years later, after his restoration as king, the 50-year-old Charles II 【requested】 a meeting with the writer and diarist Samuel Pepys.</t>
+          <t>For the next nine years, the penniless and defeated Charles 【wandered】 around Europe with only a small group of loyal supporters.</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
@@ -962,18 +962,18 @@
       <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_6b3625585e13</t>
+          <t>gi_v02_81a131241910</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -983,31 +983,31 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Customers were travelling long distances to buy supplies.</t>
+          <t>The brothers made one final attempt to produce a viable steam automobile.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Customers 【were travelling】 long distances to buy supplies.</t>
+          <t>The brothers 【made】 one final attempt to produce a viable steam automobile.</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_cb83e53d36cf</t>
+          <t>gi_v02_2fe303228461</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1017,13 +1017,13 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>So, a neural switch that automatically increases or decreases our ability to process warnings in response to changes in our environment could have been useful.</t>
+          <t>Sporting arenas have always been central to the life and culture of cities.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>So, a neural switch that automatically increases or decreases our ability to process warnings in response to changes in our environment 【could have been】 useful.</t>
+          <t>Sporting arenas 【have】 always 【been】 central to the life and culture of cities.</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a00c3026dbce</t>
+          <t>gi_v02_1bad0fc0d6b1</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1051,26 +1051,26 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>In fact, she argues that her work has been misunderstood and misapplied in a range of ways.</t>
+          <t>They recruited seventy-four 6- to 12-year-olds from Rhode Island and southern Massachusetts for the three-week study.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>In fact, she 【argues】 that her work has been misunderstood and misapplied in a range of ways.</t>
+          <t>They 【recruited】 seventy-four 6- to 12-year-olds from Rhode Island and southern Massachusetts for the three-week study.</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr"/>
     </row>
-    <row r="13" ht="44" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_a479ac7e4bac</t>
+          <t>gi_v02_f02d6ecde577</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1085,31 +1085,31 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>In their active state, phytochrome molecules bind themselves to DNA to restrict plant growth.</t>
+          <t>Steve Gloss, of the United States' Geological Survey(USGS), reckons that the chub's decline is the result of their losing their most valuable natural defense, the Colorado's rusty sediment.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>In their active state, phytochrome molecules 【bind】 themselves to DNA to restrict plant growth.</t>
+          <t>Steve Gloss, of the United States' Geological Survey(USGS), 【reckons】 that the chub's decline is the result of their losing their most valuable natural defense, the Colorado's rusty sediment.</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_b1155d36a894</t>
+          <t>gi_v02_febff3fcdd32</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1119,13 +1119,13 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Because lack of access to water can lead to starvation, disease, political instability, and even armed conflict, failure to take action can have broad and grave consequences.</t>
+          <t>Chocolate is especially popular in Europe and the United States.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Because lack of access to water can lead to starvation, disease, political instability, and even armed conflict, failure to take action 【can have】 broad and grave consequences.</t>
+          <t>Chocolate 【is】 especially popular in Europe and the United States.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
@@ -1200,13 +1200,13 @@
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
-    <row r="17" ht="44" customHeight="1">
+    <row r="17" ht="76" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_7d9017ea1dee</t>
+          <t>gi_v02_e63c9d7a60cd</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1221,31 +1221,31 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Josie says that in the last decade he has worked on over 15 buildings with the number of failures into double figures.</t>
+          <t>Perhaps the most fundamental step in developing a sense of number is not the ability to count, but rather to see that a number is really an abstract idea instead of a simple attachment to a group of particular objects.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Josie 【says】 that in the last decade he has worked on over 15 buildings with the number of failures into double figures.</t>
+          <t>Perhaps the most fundamental step in developing a sense of number 【is not】 the ability to count, but rather to see that a number is really an abstract idea instead of a simple attachment to a group of particular objects.</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
     </row>
-    <row r="18" ht="44" customHeight="1">
+    <row r="18" ht="76" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_ec4fe0a5f6cd</t>
+          <t>gi_v02_22802af7bc82</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1255,26 +1255,26 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Travelers get great joy from every step that take forward on this endless but exciting journey towards sustainability.</t>
+          <t>The aim of the present study is to start to provide such information, to help teachers design their educational strategies to build upon correct ideas and to displace misconceptions and to plan programmes in environmental studies in their schools.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Travelers 【get】 great joy from every step that take forward on this endless but exciting journey towards sustainability.</t>
+          <t>The aim of the present study 【is】 to start to provide such information, to help teachers design their educational strategies to build upon correct ideas and to displace misconceptions and to plan programmes in environmental studies in their schools.</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="44" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_228ae6a09c99</t>
+          <t>gi_v02_f938373b34cf</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1289,31 +1289,31 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The rules were gradually relaxed over the years until finally during the Qing Dynasty (1644-1911 AD), even peasants, the lowest caste, were also entitled to wear silk.</t>
+          <t>For example, studies have shown that procrastination negatively impacts student performance.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>The rules 【were】 gradually 【relaxed】 over the years until finally during the Qing Dynasty (1644-1911 AD), even peasants, the lowest caste, were also entitled to wear silk.</t>
+          <t>For example, studies 【have shown】 that procrastination negatively impacts student performance.</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
     </row>
-    <row r="20" ht="44" customHeight="1">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_e02738d53251</t>
+          <t>gi_v02_253ae4d97ab4</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1323,13 +1323,13 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>At this point in their lives, those mothers who later went on to learn to read had a similar level of child mortality (105/1000).</t>
+          <t>When the remaining two thirds of the vast open area are in production, 20 staff will harvest up to 1,000 kg of perhaps 35 different varieties of fruit and vegetables, every day.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>At this point in their lives, those mothers who later went on to learn to read 【had】 a similar level of child mortality (105/1000).</t>
+          <t>When the remaining two thirds of the vast open area are in production, 20 staff 【will harvest】 up to 1,000 kg of perhaps 35 different varieties of fruit and vegetables, every day.</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_a3c38640b493</t>
+          <t>gi_v02_5148126a70c6</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,31 +1357,31 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>The design of the entrances is based on the porcupine-quill headdresses of the local Shona tribe.</t>
+          <t>In 1999, the Marine Stewardship Council (MSC)*** commissioned a review of the Alaska salmon fishery.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The design of the entrances 【is based】 on the porcupine-quill headdresses of the local Shona tribe.</t>
+          <t>In 1999, the Marine Stewardship Council (MSC)*** 【commissioned】 a review of the Alaska salmon fishery.</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="44" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_61028905d351</t>
+          <t>gi_v02_c7832f58c54d</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1391,26 +1391,26 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>The role of the chief is crucial.</t>
+          <t>Some hotels aim to provide superior working conditions for their employees.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>The role of the chief 【is】 crucial.</t>
+          <t>Some hotels 【aim】 to provide superior working conditions for their employees.</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
     </row>
-    <row r="23" ht="44" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_b79392184908</t>
+          <t>gi_v02_3dec9a07b93e</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1425,13 +1425,13 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>This crass commercial invention gradually began to evolve as an art.</t>
+          <t>Though the hyacinth species is distinctive in appearance, another aquatic floating plant – water lettuce – is sometimes mistakenly identified as water hyacinth.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>This crass commercial invention gradually 【began】 to evolve as an art.</t>
+          <t>Though the hyacinth species is distinctive in appearance, another aquatic floating plant – water lettuce – 【is】 sometimes mistakenly 【identified】 as water hyacinth.</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3a60409fb50f</t>
+          <t>gi_v02_13106e7c204f</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1459,26 +1459,26 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>A less specific variant of the argument is that the imitation of children is imperfect: they copy their parents' speech, but never reproduce it exactly.</t>
+          <t>Couran Cove Island Resort does not conform to the characteristics of the Resort Development Spectrum, as proposed by Prideaux (2000).</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>A less specific variant of the argument 【is】 that the imitation of children is imperfect: they copy their parents' speech, but never reproduce it exactly.</t>
+          <t>Couran Cove Island Resort 【does not conform】 to the characteristics of the Resort Development Spectrum, as proposed by Prideaux (2000).</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
     </row>
-    <row r="25" ht="76" customHeight="1">
+    <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_20f3ac26fc17</t>
+          <t>gi_v02_df006dcbe14c</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1493,13 +1493,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>"When we moved to multicore—away from a linear focus on megahertz and gigahertz— and throttled down microprocessors, the energy savings were pretty substantial," says Allyson Klein, Intel's marketing manager for its Ecotech Initiative.</t>
+          <t>One is that the answer is obvious: the purpose of marketing is to sell things and to make money.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>"When we moved to multicore—away from a linear focus on megahertz and gigahertz— and throttled down microprocessors, the energy savings were pretty substantial," 【says】 Allyson Klein, Intel's marketing manager for its Ecotech Initiative.</t>
+          <t>One is that the answer is obvious: the purpose of marketing 【is】 to sell things and to make money.</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_342b3344bd9b</t>
+          <t>gi_v02_8ae43a7c65bb</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1527,13 +1527,13 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>One question that has perplexed visitors, historians and archaeologists alike ever since Bingham, is why the site seems to have been abandoned before the Spanish Conquest.</t>
+          <t>More surprising is the fact that the individual storeys of a Japanese pagoda, unlike their counterparts elsewhere, are not actually connected to each other.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>One question that has perplexed visitors, historians and archaeologists alike ever since Bingham, 【is】 why the site seems to have been abandoned before the Spanish Conquest.</t>
+          <t>More surprising 【is】 the fact that the individual storeys of a Japanese pagoda, unlike their counterparts elsewhere, are not actually connected to each other.</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_8491a346bf22</t>
+          <t>gi_v02_c12d8dc1dc7d</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1663,31 +1663,31 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>By the 1740s, about the time that infant mortality was dipping, the drink was common.</t>
+          <t>Originally scheduled to be completed in 21 months, the construction of the underground line took three years.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>By the 1740s, about the time that infant mortality was dipping, the drink 【was】 common.</t>
+          <t>Originally scheduled to be completed in 21 months, the construction of the underground line 【took】 three years.</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
     </row>
-    <row r="31" ht="60" customHeight="1">
+    <row r="31" ht="44" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_b8b85287069f</t>
+          <t>gi_v02_82bc1578713e</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1697,31 +1697,31 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>When I asked several other blind study subjects to draw a spinning wheel, one particularly clever rendition appeared repeatedly: several subjects showed the wheel's spokes as curved lines.</t>
+          <t>Tasks that are emotionally loaded or difficult, such as preparing for exams, are prime candidates for procrastination.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>When I asked several other blind study subjects to draw a spinning wheel, one particularly clever rendition appeared repeatedly: several subjects 【showed】 the wheel's spokes as curved lines.</t>
+          <t>Tasks that are emotionally loaded or difficult, such as preparing for exams, 【are】 prime candidates for procrastination.</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
     </row>
-    <row r="32" ht="44" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_d6b6676e96f8</t>
+          <t>gi_v02_9e16b461e730</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1731,13 +1731,13 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>According to researchers, the ability to trail around B&amp;Q has made the most dramatic difference to our Sundays.</t>
+          <t>Fire and flood are two of humanity's worst nightmares.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>According to researchers, the ability to trail around B&amp;Q 【has made】 the most dramatic difference to our Sundays.</t>
+          <t>Fire and flood 【are】 two of humanity's worst nightmares.</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
@@ -1778,13 +1778,13 @@
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
     </row>
-    <row r="34" ht="76" customHeight="1">
+    <row r="34" ht="44" customHeight="1">
       <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_8754400cb103</t>
+          <t>gi_v02_a3ab46d3b900</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1799,26 +1799,26 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>This means that a forest policy is vital, that it must transcend national frontiers and generations of people, and that it must allow for the inevitable changes that take place in the forests, in needs, and hence in policy.</t>
+          <t>Then the gas was released quickly into a low-pressure evaporator coil where it became liquid and cold.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>This 【means】 that a forest policy is vital, that it must transcend national frontiers and generations of people, and that it must allow for the inevitable changes that take place in the forests, in needs, and hence in policy.</t>
+          <t>Then the gas 【was released】 quickly into a low-pressure evaporator coil where it became liquid and cold.</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="44" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_134030d6103e</t>
+          <t>gi_v02_b03f7c2bb501</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1833,31 +1833,31 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Little was known about the transport demands of the rural households, so Phase I, between December 1985 and December 1987, focused on research.</t>
+          <t>As a matter of fact, the changes made to the workplace do not have to be dramatic.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Little was known about the transport demands of the rural households, so Phase I, between December 1985 and December 1987, 【focused】 on research.</t>
+          <t>As a matter of fact, the changes made to the workplace 【do not have】 to be dramatic.</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
     </row>
-    <row r="36" ht="44" customHeight="1">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_e2c3901e3f95</t>
+          <t>gi_v02_228ae6a09c99</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1867,31 +1867,31 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Freight traffic is expected to grow by a third in the next decade.</t>
+          <t>The rules were gradually relaxed over the years until finally during the Qing Dynasty (1644-1911 AD), even peasants, the lowest caste, were also entitled to wear silk.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Freight traffic 【is expected】 to grow by a third in the next decade.</t>
+          <t>The rules 【were】 gradually 【relaxed】 over the years until finally during the Qing Dynasty (1644-1911 AD), even peasants, the lowest caste, were also entitled to wear silk.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
     </row>
-    <row r="37" ht="76" customHeight="1">
+    <row r="37" ht="44" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_2c8ae7b69162</t>
+          <t>gi_v02_e2c3901e3f95</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1901,31 +1901,31 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Whilst the practice of Reiki itself is not necessarily considered potentially harmful, some medical practitioners are concerned that its benefits may be over-estimated by patients and that, as a result, they may ignore or abandon conventional treatments.</t>
+          <t>Freight traffic is expected to grow by a third in the next decade.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Whilst the practice of Reiki itself is not necessarily considered potentially harmful, some medical practitioners 【are】 concerned that its benefits may be over-estimated by patients and that, as a result, they may ignore or abandon conventional treatments.</t>
+          <t>Freight traffic 【is expected】 to grow by a third in the next decade.</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" ht="44" customHeight="1">
       <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_43efa9c2d189</t>
+          <t>gi_v02_92978ae33168</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1935,13 +1935,13 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>That is enough rock to explain the continental crust.</t>
+          <t>Good stress, or positive experiences of being challenged and rewarded, is thus cumulative in the same way as bad stress.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>That 【is】 enough rock to explain the continental crust.</t>
+          <t>Good stress, or positive experiences of being challenged and rewarded, 【is】 thus cumulative in the same way as bad stress.</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_540adb6bd39f</t>
+          <t>gi_v02_124280722813</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1969,31 +1969,31 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>It could go a long way, he says, to shifting consumers as well as farmers towards a more sustainable system of agriculture.</t>
+          <t>Scouts who had located food in a maze returned to mobilise their foraging teams.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>It 【could go】 a long way, he says, to shifting consumers as well as farmers towards a more sustainable system of agriculture.</t>
+          <t>Scouts who had located food in a maze 【returned】 to mobilise their foraging teams.</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
     </row>
-    <row r="40" ht="44" customHeight="1">
+    <row r="40" ht="76" customHeight="1">
       <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_119c45ad6b71</t>
+          <t>gi_v02_eb525508155d</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2003,13 +2003,13 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>In the same way, basic health-care is a condition of the exercise of autonomy.</t>
+          <t>The International Institute of Noise Control Engineering (I-INCE), on the advice of the World Health Organization, has established an international working party, which includes New Zealand, to evaluate noise and reverberation control for school rooms.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>In the same way, basic health-care 【is】 a condition of the exercise of autonomy.</t>
+          <t>The International Institute of Noise Control Engineering (I-INCE), on the advice of the World Health Organization, 【has established】 an international working party, which includes New Zealand, to evaluate noise and reverberation control for school rooms.</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d73827b498d0</t>
+          <t>gi_v02_e92825610d01</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2037,31 +2037,31 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Within schools, it means selecting students into a 'stream' of general ability, or 'sets' of subject-specific ability.</t>
+          <t>But in real situations the number and words are often accompanied by gestures to help resolve any confusion.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Within schools, it 【means】 selecting students into a 'stream' of general ability, or 'sets' of subject-specific ability.</t>
+          <t>But in real situations the number and words 【are】 often 【accompanied】 by gestures to help resolve any confusion.</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
     </row>
-    <row r="42" ht="44" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_c3aa21ac9eef</t>
+          <t>gi_v02_4a4edc5c40ec</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2071,13 +2071,13 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Since the project began, farmers trained in saline agriculture have reported increases of two to three more harvests per year.</t>
+          <t>This investment will be to their competitive advantage.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Since the project began, farmers trained in saline agriculture 【have reported】 increases of two to three more harvests per year.</t>
+          <t>This investment 【will be】 to their competitive advantage.</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr"/>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_3dec9a07b93e</t>
+          <t>gi_v02_cf1dc88e87bb</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2105,26 +2105,26 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Though the hyacinth species is distinctive in appearance, another aquatic floating plant – water lettuce – is sometimes mistakenly identified as water hyacinth.</t>
+          <t>Some recordings are made without the speakers being aware of the fact – a procedure that obtains very natural data, though ethical objections must be anticipated.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Though the hyacinth species is distinctive in appearance, another aquatic floating plant – water lettuce – 【is】 sometimes mistakenly 【identified】 as water hyacinth.</t>
+          <t>Some recordings 【are made】 without the speakers being aware of the fact – a procedure that obtains very natural data, though ethical objections must be anticipated.</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
     </row>
-    <row r="44" ht="76" customHeight="1">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="4" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_737330ab63fd</t>
+          <t>gi_v02_5d6766b73577</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2139,13 +2139,13 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>The author of the recently published "Information design for patient safety," Thea Swayne, tracked the journey of a medicine from manufacturing plant, through distribution warehouses, pharmacies and hospital wards, to patients' homes.</t>
+          <t>This is a misapprehension, according to the authors of the report, Professor Gal Zauberman, of the University of North Carolina, and Professor John Lynch, of Duke University.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>The author of the recently published "Information design for patient safety," Thea Swayne, 【tracked】 the journey of a medicine from manufacturing plant, through distribution warehouses, pharmacies and hospital wards, to patients' homes.</t>
+          <t>This 【is】 a misapprehension, according to the authors of the report, Professor Gal Zauberman, of the University of North Carolina, and Professor John Lynch, of Duke University.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4a4edc5c40ec</t>
+          <t>gi_v02_313031aa6d37</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2173,31 +2173,31 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>This investment will be to their competitive advantage.</t>
+          <t>It is not solely about productivity and the pace of life.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>This investment 【will be】 to their competitive advantage.</t>
+          <t>It 【is】 not solely about productivity and the pace of life.</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
     </row>
-    <row r="46" ht="36" customHeight="1">
+    <row r="46" ht="44" customHeight="1">
       <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_19c04adce82c</t>
+          <t>gi_v02_7faa23e5c223</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2207,31 +2207,31 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>The biggest problem is the role of the state.</t>
+          <t>Such neural engineering could have helped prehistoric humans to survive.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>The biggest problem 【is】 the role of the state.</t>
+          <t>Such neural engineering 【could have helped】 prehistoric humans to survive.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
     </row>
-    <row r="47" ht="44" customHeight="1">
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_aeed2a563a2a</t>
+          <t>gi_v02_f81d72aa532d</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2241,26 +2241,26 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Managers are organisational members who are responsible for the work performance of other organisational members.</t>
+          <t>Previous studies usually had just one way of linking education with economic growth – the presence of schools and printing presses, perhaps, or school enrolment, or the ability to sign names.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Managers 【are】 organisational members who are responsible for the work performance of other organisational members.</t>
+          <t>Previous studies usually 【had】 just one way of linking education with economic growth – the presence of schools and printing presses, perhaps, or school enrolment, or the ability to sign names.</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
     </row>
-    <row r="48" ht="44" customHeight="1">
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="4" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_65187fd14ce3</t>
+          <t>gi_v02_5f2566a04a22</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2275,31 +2275,31 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>The technical term for an evolutionary throwback is an 'atavism', from the Latin atavus, meaning forefather.</t>
+          <t>The Electrolux Trilobite 2.0 is a robotic vacuum cleaner that navigates its way around your floors using ultrasound, just like a bat.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>The technical term for an evolutionary throwback 【is】 an 'atavism', from the Latin atavus, meaning forefather.</t>
+          <t>The Electrolux Trilobite 2.0 【is】 a robotic vacuum cleaner that navigates its way around your floors using ultrasound, just like a bat.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="44" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_497cab717533</t>
+          <t>gi_v02_65187fd14ce3</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2309,26 +2309,26 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>The history of today's plastics begins with the discovery of a series of semi-synthetic thermoplastic materials in the mid-nineteenth century.</t>
+          <t>The technical term for an evolutionary throwback is an 'atavism', from the Latin atavus, meaning forefather.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>The history of today's plastics 【begins】 with the discovery of a series of semi-synthetic thermoplastic materials in the mid-nineteenth century.</t>
+          <t>The technical term for an evolutionary throwback 【is】 an 'atavism', from the Latin atavus, meaning forefather.</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
     </row>
-    <row r="50" ht="36" customHeight="1">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="4" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_1511aac78509</t>
+          <t>gi_v02_497cab717533</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2343,31 +2343,31 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>This is a very incomplete part of the picture.</t>
+          <t>The history of today's plastics begins with the discovery of a series of semi-synthetic thermoplastic materials in the mid-nineteenth century.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>This 【is】 a very incomplete part of the picture.</t>
+          <t>The history of today's plastics 【begins】 with the discovery of a series of semi-synthetic thermoplastic materials in the mid-nineteenth century.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
-    <row r="51" ht="44" customHeight="1">
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_26f2f4db7f13</t>
+          <t>gi_v02_5ed7d037b9fb</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2377,31 +2377,31 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>'They are probably not going to spend money to remove their satellites from space.'</t>
+          <t>The design of Bakelite objects, everything from earrings to television sets, was governed to a large extent by the technical requirements of the moulding process.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>'They 【are】 probably 【not going】 to spend money to remove their satellites from space.'</t>
+          <t>The design of Bakelite objects, everything from earrings to television sets, 【was governed】 to a large extent by the technical requirements of the moulding process.</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
     </row>
-    <row r="52" ht="36" customHeight="1">
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="4" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_1d74b68dc04a</t>
+          <t>gi_v02_5e89e3c7a096</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2411,26 +2411,26 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>By 1813, the Luddite resistance had all but vanished.</t>
+          <t>A test that is more abstract, or more quantitative, would provide a more controlled study of how cognitive processing works for different groups of people.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>By 1813, the Luddite resistance 【had】 all but 【vanished】.</t>
+          <t>A test that is more abstract, or more quantitative, 【would provide】 a more controlled study of how cognitive processing works for different groups of people.</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
     </row>
-    <row r="53" ht="60" customHeight="1">
+    <row r="53" ht="76" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c8c68f28ae4d</t>
+          <t>gi_v02_2c8ae7b69162</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2445,26 +2445,26 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Thunder, the shock wave that comes from a lightning flash, is thought to be the trigger for the torrential rain that is typical of storms.</t>
+          <t>Whilst the practice of Reiki itself is not necessarily considered potentially harmful, some medical practitioners are concerned that its benefits may be over-estimated by patients and that, as a result, they may ignore or abandon conventional treatments.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Thunder, the shock wave that comes from a lightning flash, 【is thought】 to be the trigger for the torrential rain that is typical of storms.</t>
+          <t>Whilst the practice of Reiki itself is not necessarily considered potentially harmful, some medical practitioners 【are】 concerned that its benefits may be over-estimated by patients and that, as a result, they may ignore or abandon conventional treatments.</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
     </row>
-    <row r="54" ht="36" customHeight="1">
+    <row r="54" ht="44" customHeight="1">
       <c r="A54" s="4" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_9e16b461e730</t>
+          <t>gi_v02_abc294283edd</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2479,13 +2479,13 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Fire and flood are two of humanity's worst nightmares.</t>
+          <t>Tight-fitting kurtas[1] and churidars[2] and high coiffures were a trend among women.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Fire and flood 【are】 two of humanity's worst nightmares.</t>
+          <t>Tight-fitting kurtas[1] and churidars[2] and high coiffures 【were】 a trend among women.</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr"/>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_24eed2358964</t>
+          <t>gi_v02_9dcbc77721ff</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2513,13 +2513,13 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>The valley running down to the beach is the famous world over for its view of distinctive red-tiled roofs.</t>
+          <t>However, people still choose Bondi as the satisfied destination rather than Manly.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>The valley running down to the beach 【is】 the famous world over for its view of distinctive red-tiled roofs.</t>
+          <t>However, people still 【choose】 Bondi as the satisfied destination rather than Manly.</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_82562bceb2db</t>
+          <t>gi_v02_4bab192e2184</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>G-L01 定位主句谓语</t>
+          <t>G-S01 识别谓语动词单位</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2547,31 +2547,31 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>The UN estimates that there will be 9.8 billion people living on the planet by mid-century.</t>
+          <t>The functions of the ruler are often separated from those of the priest: palace is distinguished from temple.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>The UN 【estimates】 that there will be 9.8 billion people living on the planet by mid-century.</t>
+          <t>The functions of the ruler are often separated from those of the priest: palace is 【distinguished】 from temple.</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
     </row>
-    <row r="57" ht="60" customHeight="1">
+    <row r="57" ht="44" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5d6766b73577</t>
+          <t>gi_v02_f3179b53b0e8</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2581,31 +2581,31 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>This is a misapprehension, according to the authors of the report, Professor Gal Zauberman, of the University of North Carolina, and Professor John Lynch, of Duke University.</t>
+          <t>The chemical process by which cement, the key ingredient of concrete, is created results in large quantities of carbon dioxide.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>This 【is】 a misapprehension, according to the authors of the report, Professor Gal Zauberman, of the University of North Carolina, and Professor John Lynch, of Duke University.</t>
+          <t>The chemical process by which cement, the key ingredient of concrete, is created 【results】 in large quantities of carbon dioxide.</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
     </row>
-    <row r="58" ht="36" customHeight="1">
+    <row r="58" ht="44" customHeight="1">
       <c r="A58" s="4" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_17080ee496ff</t>
+          <t>gi_v02_d6b6676e96f8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2615,26 +2615,26 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>These zones are lines of weakness, or hot spots.</t>
+          <t>According to researchers, the ability to trail around B&amp;Q has made the most dramatic difference to our Sundays.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>These zones 【are】 lines of weakness, or hot spots.</t>
+          <t>According to researchers, the ability to trail around B&amp;Q 【has made】 the most dramatic difference to our Sundays.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
     </row>
-    <row r="59" ht="44" customHeight="1">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_3c37dbbbe442</t>
+          <t>gi_v02_625460e228ef</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2649,26 +2649,26 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>As a Conservative white paper concluded in 1990, 'We know that prison is an expensive way of making bad people worse.'</t>
+          <t>They believed the scheme, which was known as the Witte Fietsenplan, was an answer to the perceived threats of air pollution and consumerism.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>As a Conservative white paper concluded in 1990, 'We 【know】 that prison is an expensive way of making bad people worse.'</t>
+          <t>They 【believed】 the scheme, which was known as the Witte Fietsenplan, was an answer to the perceived threats of air pollution and consumerism.</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
-    <row r="60" ht="76" customHeight="1">
+    <row r="60" ht="44" customHeight="1">
       <c r="A60" s="4" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_6e6e90e2a968</t>
+          <t>gi_v02_dc9ad55ac159</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2683,31 +2683,31 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>'In Manzalah Lagoon, for example, the increase in mercury, lead, copper and zinc coincided with the building of the High Dam at Aswan, the availability of cheap electricity, and the development of major power-based industries,' he says.</t>
+          <t>The Moon, with its wealth of sites, will surely be the first destination of archaeologists trained to work in space.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>'In Manzalah Lagoon, for example, the increase in mercury, lead, copper and zinc coincided with the building of the High Dam at Aswan, the availability of cheap electricity, and the development of major power-based industries,' he 【says】.</t>
+          <t>The Moon, with its wealth of sites, 【will】 surely 【be】 the first destination of archaeologists trained to work in space.</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
-    <row r="61" ht="36" customHeight="1">
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d5f8341f0173</t>
+          <t>gi_v02_0aacc678a08c</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>G-S01 识别谓语动词单位</t>
+          <t>G-L01 定位主句谓语</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2717,13 +2717,13 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>The community of Muthukandiya was involved throughout.</t>
+          <t>The one factor that was found to affect the child's development was family stress leading to a poor quality of parent-child interaction.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>The community of Muthukandiya 【was involved】 throughout.</t>
+          <t>The one factor that was found to affect the child's development 【was】 family stress leading to a poor quality of parent-child interaction.</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr"/>
@@ -2815,102 +2815,102 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_06ad5d601263</t>
+          <t>gi_v02_6876a73e839d</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Even as our ability to monitor space objects increases, so too does the total number of items in orbit.</t>
+          <t>The earliest indication of silk paper being used was discovered in the tomb of a noble who is estimated to have died around 168 AD.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>【Even as our ability to monitor space objects increases】, so too does the total number of items in orbit.</t>
+          <t>The earliest indication of silk paper being used was discovered in the tomb of a noble 【who is estimated to have died around 168 AD】.</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
     </row>
-    <row r="3" ht="76" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_df35371160dd</t>
+          <t>gi_v02_94ede4e18299</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>While there were good reasons for that early emphasis, an exclusive focus on what is wrong, rather than also looking at what is right and how these aspects could be further developed, is seriously shortsighted.</t>
+          <t>The scroll names celebrations that indicate shifts in seasons and details two yearly religious events known from another Dead Sea Scroll.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>【While there were good reasons for that early emphasis】, an exclusive focus on what is wrong, rather than also looking at what is right and how these aspects could be further developed, is seriously shortsighted.</t>
+          <t>The scroll names celebrations 【that indicate shifts in seasons】 and details two yearly religious events known from another Dead Sea Scroll.</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="5" t="inlineStr"/>
     </row>
-    <row r="4" ht="44" customHeight="1">
+    <row r="4" ht="76" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_67c1d9f4472a</t>
+          <t>gi_v02_24da0753fffe</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Similarly, if you employed the 'principles of marketing' in an unprincipled way, you would not be doing marketing.</t>
+          <t>However, they guarded the skills and technology required to make glass very closely, and it was not until their empire collapsed in 476 AD that glass-making knowledge became widespread throughout Europe and the Middle East.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Similarly, 【if you employed the 'principles of marketing' in an unprincipled way】, you would not be doing marketing.</t>
+          <t>However, they guarded the skills and technology required to make glass very closely, and it was not until their empire collapsed in 476 AD that 【glass-making knowledge became widespread throughout Europe and the Middle East】.</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_a2a151f15a75</t>
+          <t>gi_v02_6c3c4484af12</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2938,47 +2938,47 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>This is a literal translation of the figures (in Italian lira), yet it is the dollar with which the English-speaking audience would associate.</t>
+          <t>Whether academic research actually produces anything that is useful to the practice of business, or even whether it is its job to do so, are questions that can provoke vigorous arguments on campus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>This is a literal translation of the figures (in Italian lira), yet it is the dollar 【with which the English-speaking audience would associate】.</t>
+          <t>Whether academic research actually produces anything that is useful to the practice of business, or even whether it is its job to do so, are questions 【that can provoke vigorous arguments on campus】.</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr"/>
     </row>
-    <row r="6" ht="44" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_042087023332</t>
+          <t>gi_v02_6256648996aa</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Well above the treeline in Norway's highest mountains, ancient fields of ice are shrinking as Earth's climate warms.</t>
+          <t>Systems not only need to cope with physical challenges such as noise, they will also need to be socially aware by addressing people in the right way.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Well above the treeline in Norway's highest mountains, ancient fields of ice are shrinking 【as Earth's climate warms】.</t>
+          <t>Systems not only need to cope with physical challenges such as noise, 【they will also need to be socially aware】 by addressing people in the right way.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
@@ -2991,28 +2991,28 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e7b1dc930296</t>
+          <t>gi_v02_2e5fe39dd88f</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Where once a board schedule may have consisted of between eight and ten meetings a year, in many companies the number of events requiring board input and decisions has dramatically risen.</t>
+          <t>In Norway, after an intervention campaign was introduced nationally, an evaluation of forty-two schools suggested that, over a two-year period, bullying was halved.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>【Where once a board schedule may have consisted of between eight and ten meetings a year】, in many companies the number of events requiring board input and decisions has dramatically risen.</t>
+          <t>In Norway, after an intervention campaign was introduced nationally, an evaluation of forty-two schools suggested 【that, over a two-year period, bullying was halved】.</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -3025,28 +3025,28 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_ae4e99e067c1</t>
+          <t>gi_v02_7b23aa422cdd</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Veil Albert Kallio, a Finnish scientist, says that such an idea is impractical, because the force of the ice would ultimately snap the cables and rapidly release a large quantity of frozen ice into the sea.</t>
+          <t>The fact that our companionship with dogs now appears to go back at least 100,000 years means that this partnership may have played an important part in the development of human hunting techniques that developed 70,000 to 90,000 years ago.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Veil Albert Kallio, a Finnish scientist, says 【that such an idea is impractical】, because the force of the ice would ultimately snap the cables and rapidly release a large quantity of frozen ice into the sea.</t>
+          <t>The fact that our companionship with dogs now appears to go back at least 100,000 years means that this partnership may have played an important part in the development of human hunting techniques 【that developed 70,000 to 90,000 years ago】.</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
@@ -3059,28 +3059,28 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_14851b9ac5f7</t>
+          <t>gi_v02_554dc70ab08e</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>When old enough to leave the pouch, the young stayed in a lair such as a deep rocky cave, well-hidden nest or hollow log, whilst the mother hunted.</t>
+          <t>Those speeches fired the young chemist's enthusiasm further, and he later went on to attend the Royal College of Chemistry, which he succeeded in entering in 1853, at the age of 15.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>When old enough to leave the pouch, the young stayed in a lair such as a deep rocky cave, well-hidden nest or hollow log, 【whilst the mother hunted】.</t>
+          <t>Those speeches fired the young chemist's enthusiasm further, and 【he later went on to attend the Royal College of Chemistry】, which he succeeded in entering in 1853, at the age of 15.</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -3093,28 +3093,28 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_c111a7f66407</t>
+          <t>gi_v02_27b44d41fa13</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Hyperinflation and lack of foreign exchange make it hard to buy seeds and fertiliser, while fuel shortages stymie crop transport.</t>
+          <t>They can still reproduce even when old, and they never get cancer.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Hyperinflation and lack of foreign exchange make it hard to buy seeds and fertiliser, 【while fuel shortages stymie crop transport】.</t>
+          <t>They can still reproduce even when old, and 【they never get cancer】.</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4ea6ad4aa7c8</t>
+          <t>gi_v02_47b9b6cfb2b3</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3142,13 +3142,13 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>If current trends continue, we will raise atmospheric CO2 concentrations to double pre-industrial levels during this century.</t>
+          <t>The qanat construction method was usually faster than the counter-excavation method as it was more straightforward.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>【If current trends continue】, we will raise atmospheric CO2 concentrations to double pre-industrial levels during this century.</t>
+          <t>The qanat construction method was usually faster than the counter-excavation method 【as it was more straightforward】.</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -3161,28 +3161,28 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_fb1c647a1e9e</t>
+          <t>gi_v02_dbe821096ca5</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C10 状语从句：识别与边界</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Other studies show that keeping a dog as a pet gives children early exposure to a diverse range of bacteria, which may help protect them against allergies later.</t>
+          <t>Whereas the region's native evergreen pines shade the snow and absorb radiation, birches would shed their leaves in winter, thus enabling radiation to be reflected by the snow.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Other studies show 【that keeping a dog as a pet gives children early exposure to a diverse range of bacteria】, which may help protect them against allergies later.</t>
+          <t>【Whereas the region's native evergreen pines shade the snow and absorb radiation】, birches would shed their leaves in winter, thus enabling radiation to be reflected by the snow.</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_8f1b84722c49</t>
+          <t>gi_v02_22557b4de89a</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3210,60 +3210,60 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Kirsh argues that by using the body to simulate outcomes, McGregor is able to imagine solutions that would not be possible using purely abstract thought.</t>
+          <t>This group had inferred that success or failure is due to innate ability, and this 'fixed mindset' had led them to fear of failure and lack of effort.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Kirsh argues 【that by using the body to simulate outcomes, McGregor is able to imagine solutions】 that would not be possible using purely abstract thought.</t>
+          <t>This group had inferred 【that success or failure is due to innate ability】, and this 'fixed mindset' had led them to fear of failure and lack of effort.</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_7db1c1d381c0</t>
+          <t>gi_v02_88e0f721fc1c</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>The theory sounds eccentric but once he starts to explain the detective work that went into his deduction, the skepticism gives way to wary admiration.</t>
+          <t>But there are many ways athletes can ensure they respond positively under pressure.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>The theory sounds eccentric but once he starts to explain the detective work 【that went into his deduction】, the skepticism gives way to wary admiration.</t>
+          <t>But there are many ways athletes can ensure 【they respond positively under pressure】.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
     </row>
-    <row r="15" ht="44" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_ba8852fcbfea</t>
+          <t>gi_v02_11e2f18b3802</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3278,81 +3278,81 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>The primary reason for the search is basic curiosity—the same curiosity about the natural world that drives all pure science.</t>
+          <t>The second group – those who had been instilled with a 'growth mindset' – were subsequently far more likely to put effort into future tasks.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The primary reason for the search is basic curiosity—the same curiosity about the natural world 【that drives all pure science】.</t>
+          <t>The second group – those 【who had been instilled with a 'growth mindset'】 – were subsequently far more likely to put effort into future tasks.</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr"/>
     </row>
-    <row r="16" ht="44" customHeight="1">
+    <row r="16" ht="76" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_f43069ab4b92</t>
+          <t>gi_v02_8b9d0f942c5c</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>G-C02 并列分句</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Prior to this, gunpowder was used, but this was limited and clumsy.</t>
+          <t>After a stressful public event, such as a natural disaster or major financial crash, there is often a wave of alarming information in traditional and social media, which individuals become very aware of.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Prior to this, gunpowder was used, but 【this was limited and clumsy】.</t>
+          <t>After a stressful public event, such as a natural disaster or major financial crash, there is often a wave of alarming information in traditional and social media, 【which individuals become very aware of】.</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="76" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4e8c10ffae02</t>
+          <t>gi_v02_5e191c40a6b0</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C10 状语从句：识别与边界</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>The idea is modelled on historic volcanic explosions, such as that of Mount Pinatubo in the Philippines in 1991, which led to a short-term cooling of global temperatures by 0.5 °C.</t>
+          <t>Studies reveal that if a layer of air of about five centimetres could be held in place close to the skin, it would provide the same insulation as does the impressively dense winter coat of the arctic fox.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The idea is modelled on historic volcanic explosions, such as that of Mount Pinatubo in the Philippines in 1991, 【which led to a short-term cooling of global temperatures by 0.5 °C】.</t>
+          <t>Studies reveal that 【if a layer of air of about five centimetres could be held in place close to the skin】, it would provide the same insulation as does the impressively dense winter coat of the arctic fox.</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -3365,28 +3365,28 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_732e64d24d4d</t>
+          <t>gi_v02_40e8d9538a79</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>G-C02 并列分句</t>
+          <t>G-C10 状语从句：识别与边界</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Rarely do patients watch a doctor write with a pen that isn't emblazoned with a drug's name, or see a nurse use a tablet not bearing a pharmaceutical company's logo.</t>
+          <t>Most stepwells are found dotted round the desert areas of Gujarat (where they are called vav) and Rajasthan (where they are called baori), while a few also survive in Delhi.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Rarely do patients watch a doctor write with a pen that isn't emblazoned with a drug's name, or 【see a nurse use a tablet not bearing a pharmaceutical company's logo】.</t>
+          <t>Most stepwells are found dotted round the desert areas of Gujarat (where they are called vav) and Rajasthan (where they are called baori), 【while a few also survive in Delhi】.</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
@@ -3399,28 +3399,28 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_29a565605c6a</t>
+          <t>gi_v02_bf65352b0423</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>When dealers tried to punish NPM users by paying less for NPM cotton, the farmers united to form a marketing cooperative that found fairer prices elsewhere.</t>
+          <t>It follows that the international community should address the issue of 'disaster preparedness' and establish a process by which natural disasters are dealt with.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>When dealers tried to punish NPM users by paying less for NPM cotton, the farmers united to form a marketing cooperative 【that found fairer prices elsewhere】.</t>
+          <t>It follows that the international community should address the issue of 'disaster preparedness' and 【establish a process】 by which natural disasters are dealt with.</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
@@ -3433,41 +3433,41 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_fd81b2e04036</t>
+          <t>gi_v02_a5237288d225</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>The displays of art museums serve as a warning of what critical practices can emerge when spontaneous criticism is suppressed.</t>
+          <t>In his opinion, humans domesticated dogs and dogs domesticated humans.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>The displays of art museums serve as a warning of what critical practices can emerge 【when spontaneous criticism is suppressed】.</t>
+          <t>In his opinion, humans domesticated dogs and 【dogs domesticated humans】.</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
     </row>
-    <row r="21" ht="44" customHeight="1">
+    <row r="21" ht="92" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_a3b52ae0a74b</t>
+          <t>gi_v02_834fd13d204e</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3482,94 +3482,94 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>The Painting Fool is one of a growing number of computer programs which, so their makers claim, possess creative talents.</t>
+          <t>Engineers are tasked with changing how we travel round cities through urban design, but the engineering industry still works on the assumptions that led to the creation of the energy-consuming transport systems we have now: the emphasis placed solely on efficiency, speed, and quantitative data.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The Painting Fool is one of a growing number of computer programs 【which, so their makers claim, possess creative talents】.</t>
+          <t>Engineers are tasked with changing how we travel round cities through urban design, but the engineering industry still works on the assumptions 【that led to the creation of the energy-consuming transport systems we have now】: the emphasis placed solely on efficiency, speed, and quantitative data.</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="92" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_51ed76db671d</t>
+          <t>gi_v02_6499f9fe6fad</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Since only fresh water freezes into ice, the water that remains becomes increasingly salty and dense, sinking until it spills over the continental shelf.</t>
+          <t>Professor Short contends the mindset and skill-sets behind these designs have been completely lost, lamenting the disappearance of expertly designed theatres, opera houses, and other buildings where up to half the volume of the building was given over to ensuring everyone got fresh air.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Since only fresh water freezes into ice, the water 【that remains】 becomes increasingly salty and dense, sinking until it spills over the continental shelf.</t>
+          <t>Professor Short contends 【the mindset and skill-sets behind these designs have been completely lost】, lamenting the disappearance of expertly designed theatres, opera houses, and other buildings where up to half the volume of the building was given over to ensuring everyone got fresh air.</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
     </row>
-    <row r="23" ht="76" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_674a0576bea2</t>
+          <t>gi_v02_f6e71b2bc4da</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C10 状语从句：识别与边界</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>'A further risk with geo-engineering projects is that you can "overshoot",' says Dr Dan Lunt, from the University of Bristol's School of Geophysical Sciences, who has studied the likely impacts of the sunshade and aerosol schemes on the climate.</t>
+          <t>On the other hand, they found that children of 15 to 18 months are generally not able to recognize themselves unless other cues such as movement are present.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>'A further risk with geo-engineering projects is 【that you can "overshoot"】,' says Dr Dan Lunt, from the University of Bristol's School of Geophysical Sciences, who has studied the likely impacts of the sunshade and aerosol schemes on the climate.</t>
+          <t>On the other hand, they found that children of 15 to 18 months are generally not able to recognize themselves 【unless other cues such as movement are present】.</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="44" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_625d529e44af</t>
+          <t>gi_v02_aca72e90ce2d</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3584,81 +3584,81 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Direct food distribution systems not only encourage small-scale agriculture but also give consumers more control over the food they consume, she wrote.</t>
+          <t>EPRI, which is funded by power companies, is looking at ways to protect the United States' power grid from lightning strikes.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Direct food distribution systems not only encourage small-scale agriculture but also give consumers more control over the food 【they consume】, she wrote.</t>
+          <t>EPRI, 【which is funded by power companies】, is looking at ways to protect the United States' power grid from lightning strikes.</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
     </row>
-    <row r="25" ht="92" customHeight="1">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_0351cf44000e</t>
+          <t>gi_v02_04a70ae710a6</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>The orbital cortex, the region that becomes active in Goel's experiment, seems the best candidate for the site that feeds such feelings into higher-level thought processes, with its close connections to the brain's sub-cortical arousal apparatus and centres of metabolic control.</t>
+          <t>The situation has already changed near the main townships, and there has long been a scarcity of land for cultivation in the Valley.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The orbital cortex, the region that becomes active in Goel's experiment, seems the best candidate for the site 【that feeds such feelings into higher-level thought processes】, with its close connections to the brain's sub-cortical arousal apparatus and centres of metabolic control.</t>
+          <t>The situation has already changed near the main townships, and 【there has long been a scarcity of land for cultivation in the Valley】.</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
     </row>
-    <row r="26" ht="76" customHeight="1">
+    <row r="26" ht="44" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3a0f192d91dc</t>
+          <t>gi_v02_76db8cbc0923</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>A general declaration was made that 'a central place in any ecologically coherent forest policy must be given to continuity over time and to the possible effects of unforeseen events, to ensure that the full potential of these forests is maintained'.</t>
+          <t>Most contestants claim to have just average memories, and scientific testing confirms that they're not just being modest.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>A general declaration was made that 'a central place in any ecologically coherent forest policy must be given to continuity over time and to the possible effects of unforeseen events, 【to ensure that the full potential of these forests is maintained】'.</t>
+          <t>Most contestants claim to have just average memories, and scientific testing confirms 【that they're not just being modest】.</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
@@ -3671,28 +3671,28 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_8d6b78d3394d</t>
+          <t>gi_v02_7e281eaed9d3</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>One difficulty here is defining what these areas should conserve: areas where the greatest soil diversity is present?</t>
+          <t>Fosbury himself did not know what he was doing.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>One difficulty here is defining what these areas should conserve: areas 【where the greatest soil diversity is present】?</t>
+          <t>Fosbury himself did not know 【what he was doing】.</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
@@ -3705,28 +3705,28 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_ecccbd122c70</t>
+          <t>gi_v02_4addd753b15b</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C10 状语从句：识别与边界</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Furthermore, they thought that only a lunatic fringe of about one in 1,000 would give the highest shock of 450 volts.</t>
+          <t>'It's very clear when you look at twins that much of what they share is hardwired,' she says.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Furthermore, they thought 【that only a lunatic fringe of about one in 1,000 would give the highest shock of 450 volts】.</t>
+          <t>'It's very clear 【when you look at twins】 that much of what they share is hardwired,' she says.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
@@ -3739,75 +3739,75 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_696f8298d678</t>
+          <t>gi_v02_a17290f02a9f</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Instead we should realise we have a symbiotic relationship, that can be mutually beneficial or mutually destructive.</t>
+          <t>There are no pictures showing the construction of the pyramids, so there is no way to tell what really happened.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Instead we should realise we have a symbiotic relationship, 【that can be mutually beneficial or mutually destructive】.</t>
+          <t>There are no pictures showing the construction of the pyramids, so there is no way to tell 【what really happened】.</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="44" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3f60dd8febfe</t>
+          <t>gi_v02_c9787aefee0a</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Numerous studies in both animals and humans have shown that a mother's obesity directly increases her child's risk for weight gain.</t>
+          <t>In the last decade of the millennium, the market shrank and ethnic wear made a comeback.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Numerous studies in both animals and humans have shown 【that a mother's obesity directly increases her child's risk for weight gain】.</t>
+          <t>In the last decade of the millennium, the market shrank and 【ethnic wear made a comeback】.</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
     </row>
-    <row r="31" ht="44" customHeight="1">
+    <row r="31" ht="76" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5a13cdff0547</t>
+          <t>gi_v02_00976c9910ab</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3822,26 +3822,26 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>"It gives science back to the poor, to the people who really need it."</t>
+          <t>It was known in biblical times, and is mentioned in several books of the Bible, both as an ingredient that was mixed with oils for anointing people's bodies, and also as a token indicating friendship among lovers and friends.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>"It gives science back to the poor, to the people 【who really need it】."</t>
+          <t>It was known in biblical times, and is mentioned in several books of the Bible, both as an ingredient 【that was mixed with oils for anointing people's bodies】, and also as a token indicating friendship among lovers and friends.</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="44" customHeight="1">
       <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a18ff98dd27e</t>
+          <t>gi_v02_0f82546e778f</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3856,60 +3856,60 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>More immediately, conservationists can arm themselves with all this knowledge to spot the warning signs of species that may be at risk.</t>
+          <t>Alternative explorations – where experimentation and human instinct lead to progress and new ideas – are effectively discouraged.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>More immediately, conservationists can arm themselves with all this knowledge to spot the warning signs of species 【that may be at risk】.</t>
+          <t>Alternative explorations – 【where experimentation and human instinct lead to progress and new ideas】 – are effectively discouraged.</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
     </row>
-    <row r="33" ht="44" customHeight="1">
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_63c29b9bc9e1</t>
+          <t>gi_v02_3d724945dd14</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>And when obese people lose weight, their leptin levels plummet along with their metabolism.</t>
+          <t>The wasp has only a few minutes to prepare its next sting, in the exact area of the brain which controls the cockroaches' instinct to escape.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>And 【when obese people lose weight】, their leptin levels plummet along with their metabolism.</t>
+          <t>The wasp has only a few minutes to prepare its next sting, in the exact area of the brain 【which controls the cockroaches' instinct to escape】.</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
     </row>
-    <row r="34" ht="44" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_827f1d040157</t>
+          <t>gi_v02_f5feabf3f41b</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3924,47 +3924,47 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>As a result, certain habitats disappeared, and species that had once formed communities split apart.</t>
+          <t>However, in the four decades since the building of the Glen Canyon dam, just upstream of the Grand Canyon, the only sediment that it has collected has come from tiny, undammed tributaries.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>As a result, certain habitats disappeared, and species 【that had once formed communities】 split apart.</t>
+          <t>However, in the four decades since the building of the Glen Canyon dam, just upstream of the Grand Canyon, the only sediment 【that it has collected】 has come from tiny, undammed tributaries.</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
     </row>
-    <row r="35" ht="76" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_00736a85e43b</t>
+          <t>gi_v02_1d2642325db5</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Nwanze, Murphy and Fan argued that private risk management tools, like private insurance, commodity futures markets, and rural finance can help small-scale producers mitigate risk and allow for investment in improvements.</t>
+          <t>This is the graduate that governments will be calling upon to shift the community focus from medical dependency to healthy lifestyles in the decades ahead.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Nwanze, Murphy and Fan argued 【that private risk management tools, like private insurance, commodity futures markets, and rural finance can help small-scale producers mitigate risk and allow for investment in improvements】.</t>
+          <t>This is the graduate 【that governments will be calling upon】 to shift the community focus from medical dependency to healthy lifestyles in the decades ahead.</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
@@ -3977,177 +3977,177 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_2ffbde5b441a</t>
+          <t>gi_v02_3272aad438e5</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>The wrong kind of leadership will lead to what Cialdini calls 'captainitis,' the regrettable tendency of team members to opt out of team responsibilities that are properly theirs.</t>
+          <t>The universities which prepare students for our changing future have little choice but to change with new trends and new standards.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>The wrong kind of leadership will lead to 【what Cialdini calls 'captainitis,'】 the regrettable tendency of team members to opt out of team responsibilities that are properly theirs.</t>
+          <t>The universities 【which prepare students for our changing future】 have little choice but to change with new trends and new standards.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
     </row>
-    <row r="37" ht="92" customHeight="1">
+    <row r="37" ht="44" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_db5f3603425c</t>
+          <t>gi_v02_ee8993465ce6</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Descartes argued that a person only accepts or rejects information after considering its truth or falsehood; Spinoza argued that people accept all encountered information (or misinformation) by default and then subsequently verify or reject it through a separate cognitive process.</t>
+          <t>CO2 is a greenhouse gas that traps the Sun's radiation within the troposphere, the lower atmosphere.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Descartes argued 【that a person only accepts or rejects information after considering its truth or falsehood】; Spinoza argued that people accept all encountered information (or misinformation) by default and then subsequently verify or reject it through a separate cognitive process.</t>
+          <t>CO2 is a greenhouse gas 【that traps the Sun's radiation within the troposphere】, the lower atmosphere.</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
     </row>
-    <row r="38" ht="76" customHeight="1">
+    <row r="38" ht="44" customHeight="1">
       <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_c5630ab09091</t>
+          <t>gi_v02_56cf10c33821</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>In 2005 the computers of the world ate up 123 billion kilowatt-hours of energy, a number that will double by 2010 if present trends continue, according to Jonathan Koomey, a staff scientist at Lawrence Berkeley National Laboratory.</t>
+          <t>So many variables enter into the equation, and our understanding in many cases is fundamental.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>In 2005 the computers of the world ate up 123 billion kilowatt-hours of energy, a number 【that will double by 2010】 if present trends continue, according to Jonathan Koomey, a staff scientist at Lawrence Berkeley National Laboratory.</t>
+          <t>So many variables enter into the equation, and 【our understanding in many cases is fundamental】.</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
     </row>
-    <row r="39" ht="60" customHeight="1">
+    <row r="39" ht="76" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_01b8a6c456fa</t>
+          <t>gi_v02_f522b6890b14</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Its main selling point is that unlike standard desalination techniques, it doesn't require a generated power supply: just sunlight.</t>
+          <t>A further argument against the simple wear and tear theory is the observation that the time within which organisms age lies between a few days (even a few hours for unicellular organisms) and several thousand years, as with mammoth trees.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Its main selling point is 【that unlike standard desalination techniques, it doesn't require a generated power supply: just sunlight】.</t>
+          <t>A further argument against the simple wear and tear theory is the observation that the time 【within which organisms age】 lies between a few days (even a few hours for unicellular organisms) and several thousand years, as with mammoth trees.</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
     </row>
-    <row r="40" ht="92" customHeight="1">
+    <row r="40" ht="76" customHeight="1">
       <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_9682f5253a18</t>
+          <t>gi_v02_5f897bea52d5</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>G-C02 并列分句</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>That is not to suggest everyone should dance their way to work, however healthy and happy it might make us, but rather that the techniques used by choreographers to experiment with and design movement in dance could provide engineers with tools to stimulate new ideas in city-making.</t>
+          <t>An overriding question for developmental economists remains whether the upswing will continue so Africans can grow their way out of poverty that relegates some 40 percent of the nearly 744 million in that region to living on less than a dollar a day.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>That is not to suggest everyone should dance their way to work, however healthy and happy it might make us, but 【rather that the techniques used by choreographers to experiment with and design movement in dance could provide engineers with tools】 to stimulate new ideas in city-making.</t>
+          <t>An overriding question for developmental economists remains whether the upswing will continue so Africans can grow their way out of poverty 【that relegates some 40 percent of the nearly 744 million in that region to living on less than a dollar a day】.</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
     </row>
-    <row r="41" ht="44" customHeight="1">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_2fe24b305749</t>
+          <t>gi_v02_ea5e5571413b</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4162,26 +4162,26 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>In Stockholm, car use has actually fallen in recent years as the city has become larger and wealthier.</t>
+          <t>The research, which focused on children aged five to fifteen, discovered that those who slept late on Saturdays and Sundays decreased the probability of having weight problems as they grew up.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>In Stockholm, car use has actually fallen in recent years 【as the city has become larger and wealthier】.</t>
+          <t>The research, which focused on children aged five to fifteen, discovered that those who slept late on Saturdays and Sundays decreased the probability of having weight problems 【as they grew up】.</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
     </row>
-    <row r="42" ht="92" customHeight="1">
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_b76a67e4e1b9</t>
+          <t>gi_v02_25ca2bb75c3d</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4196,13 +4196,13 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>One of the reasons why the enthusiasm for rewilding is spreading so quickly in Britain is that it helps to create a more inspiring vision than the green movement's usual promise of 'Follow us and the world will be slightly less awful than it would otherwise have been.'</t>
+          <t>At the moment, though, more needs to be done to reduce the detrimental impact it would have on the environment, particularly as regards the use of energy.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>One of the reasons 【why the enthusiasm for rewilding is spreading so quickly in Britain】 is that it helps to create a more inspiring vision than the green movement's usual promise of 'Follow us and the world will be slightly less awful than it would otherwise have been.'</t>
+          <t>At the moment, though, more needs to be done to reduce the detrimental impact 【it would have on the environment】, particularly as regards the use of energy.</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr"/>
@@ -4215,41 +4215,41 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_f966c3622221</t>
+          <t>gi_v02_7cec24d111f8</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>'If you are in a state of mind-wandering you are not bored,' he says.</t>
+          <t>So, I do all I can to keep these pests away.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>'【If you are in a state of mind-wandering】 you are not bored,' he says.</t>
+          <t>So, I do all 【I can】 to keep these pests away.</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
     </row>
-    <row r="44" ht="44" customHeight="1">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="4" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_947fac925d0f</t>
+          <t>gi_v02_a1a945b2fd62</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4264,81 +4264,81 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Despite all this, there is limited empirical evidence to suggest that streaming results in better outcomes for students.</t>
+          <t>While physicists have demonstrated entanglement with specially prepared atoms, no-one knows if it also exists between atoms making up human minds.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Despite all this, there is limited empirical evidence to suggest 【that streaming results in better outcomes for students】.</t>
+          <t>While physicists have demonstrated entanglement with specially prepared atoms, no-one knows 【if it also exists between atoms making up human minds】.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
     </row>
-    <row r="45" ht="44" customHeight="1">
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_1829809f5482</t>
+          <t>gi_v02_6c8587c33a22</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>The study suggests that playing action video games primes the brain to make quick decisions.</t>
+          <t>'However, we also want to highlight the research and conservation efforts that are now being carried out to try to save them from the threat of global warming.'</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>The study suggests 【that playing action video games primes the brain to make quick decisions】.</t>
+          <t>'However, we also want to highlight the research and conservation efforts 【that are now being carried out】 to try to save them from the threat of global warming.'</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
     </row>
-    <row r="46" ht="76" customHeight="1">
+    <row r="46" ht="44" customHeight="1">
       <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_566a875c53ba</t>
+          <t>gi_v02_b2ca3fd0f245</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>My colleagues and I devised a scale to measure proneness to feeling regret, and we found that people with high sensitivity to regret are less happy, less satisfied with life, less optimistic and more depressed than those with low sensitivity.</t>
+          <t>Jah illustrates this with a web-based database that he has developed.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>My colleagues and I devised a scale to measure proneness to feeling regret, and we found 【that people with high sensitivity to regret are less happy, less satisfied with life, less optimistic and more depressed than those with low sensitivity】.</t>
+          <t>Jah illustrates this with a web-based database 【that he has developed】.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
@@ -4351,75 +4351,75 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_ed8fb1baf64e</t>
+          <t>gi_v02_b2a2c2f0d2e5</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C02 并列分句</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>The history of childhood has been a heated topic in social history since the highly influential book 'Centuries of Childhood', written by French historian Philippe Aries, emerged in 1960.</t>
+          <t>Even if voice-morphing technology simulates the speaker's voice, their lip movements won't match, and they will look like they are in a dubbed movie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>The history of childhood has been a heated topic in social history 【since the highly influential book 'Centuries of Childhood', written by French historian Philippe Aries, emerged in 1960】.</t>
+          <t>Even if voice-morphing technology simulates the speaker's voice, their lip movements won't match, and 【they will look like they are in a dubbed movie】.</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
     </row>
-    <row r="48" ht="60" customHeight="1">
+    <row r="48" ht="44" customHeight="1">
       <c r="A48" s="4" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_b2b71f0819f1</t>
+          <t>gi_v02_f069ab0d254c</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>First, Neolithic* Britons used primitive tools, which may have been fashioned out of deer antlers, to dig a massive circular ditch and bank, or henge.</t>
+          <t>This complicated process and questionable outcome begs the question: what is the actual point of this technology?</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>First, Neolithic* Britons used primitive tools, 【which may have been fashioned out of deer antlers】, to dig a massive circular ditch and bank, or henge.</t>
+          <t>This complicated process and questionable outcome begs the question: 【what is the actual point of this technology】?</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="44" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c296d5b76634</t>
+          <t>gi_v02_13a07d8165f7</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4434,13 +4434,13 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>What are we to do, then, when confronted with situations like a disagreement with a spouse or negotiating a contract at work, that require us to take a personal stake?</t>
+          <t>Whenever a sought-for answer snaps into place, there is a shudder of pleased recognition.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>What are we to do, then, 【when confronted with situations like a disagreement with a spouse or negotiating a contract at work】, that require us to take a personal stake?</t>
+          <t>【Whenever a sought-for answer snaps into place】, there is a shudder of pleased recognition.</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
@@ -4453,62 +4453,62 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_9e6b4d4833c2</t>
+          <t>gi_v02_e2612c325ed9</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>G-C02 并列分句</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Lessons last for a standardised 50 minutes and are always followed by a 10-minute break, which gives the pupils a chance to let off steam.</t>
+          <t>The conviction that historical relics provide infallible testimony about the past is rooted in the nineteenth and early twentieth centuries, when science was regarded as objective and value free.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Lessons last for a standardised 50 minutes and 【are always followed by a 10-minute break】, which gives the pupils a chance to let off steam.</t>
+          <t>The conviction that historical relics provide infallible testimony about the past is rooted in the nineteenth and early twentieth centuries, 【when science was regarded as objective and value free】.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
     </row>
-    <row r="51" ht="60" customHeight="1">
+    <row r="51" ht="76" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4458d2f92b62</t>
+          <t>gi_v02_d1e54f398f2d</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Similarly, Colton thinks that when people experience art, they wonder what the artist might have been thinking or what the artist is trying to tell them.</t>
+          <t>This means that a forest policy is vital, that it must transcend national frontiers and generations of people, and that it must allow for the inevitable changes that take place in the forests, in needs, and hence in policy.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Similarly, Colton thinks that 【when people experience art】, they wonder what the artist might have been thinking or what the artist is trying to tell them.</t>
+          <t>This means that a forest policy is vital, that it must transcend national frontiers and generations of people, and that it must allow for the inevitable changes 【that take place in the forests, in needs, and hence in policy】.</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
@@ -4521,28 +4521,28 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_8b614852c8bd</t>
+          <t>gi_v02_873d0ba0a5bb</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>The fortunes of wetlands would be improved, Silvius suggests, if more governments recognised their long-term value.</t>
+          <t>Most innovative products – those that create new product categories or revolutionize old ones – are also unsuccessful.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>The fortunes of wetlands would be improved, Silvius suggests, 【if more governments recognised their long-term value】.</t>
+          <t>Most innovative products – those 【that create new product categories or revolutionize old ones】 – are also unsuccessful.</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
@@ -4555,28 +4555,28 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_ac5a768b2a7e</t>
+          <t>gi_v02_21ed2c4194bb</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>People from the eastern world questioned the argument as not being logical, because in their knowledge some furry animals just don't hibernate.</t>
+          <t>'The Green Mountain system is a man-made system that has produced a tropical rainforest without any co-evolution between its constituent species,' says Wilkinson.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>People from the eastern world questioned the argument as not being logical, 【because in their knowledge some furry animals just don't hibernate】.</t>
+          <t>'The Green Mountain system is a man-made system 【that has produced a tropical rainforest without any co-evolution between its constituent species】,' says Wilkinson.</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
@@ -4589,41 +4589,41 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_40e8d9538a79</t>
+          <t>gi_v02_82ae447e8528</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C04 定语从句：边界与先行词</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Most stepwells are found dotted round the desert areas of Gujarat (where they are called vav) and Rajasthan (where they are called baori), while a few also survive in Delhi.</t>
+          <t>For New Zealand, the emission of carbon dioxide only accounts for 0.5% of the world's total, which has met the governmental standard.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Most stepwells are found dotted round the desert areas of Gujarat (where they are called vav) and Rajasthan (where they are called baori), 【while a few also survive in Delhi】.</t>
+          <t>For New Zealand, the emission of carbon dioxide only accounts for 0.5% of the world's total, 【which has met the governmental standard】.</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
     </row>
-    <row r="55" ht="76" customHeight="1">
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e684c2b4474a</t>
+          <t>gi_v02_7db1c1d381c0</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4638,81 +4638,81 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>With exceptionally keen powers of observation and great finesse with a paintbrush, she recorded subtle nuances of colour, shape, and light that enlivened her paintings and attracted a wide audience.</t>
+          <t>The theory sounds eccentric but once he starts to explain the detective work that went into his deduction, the skepticism gives way to wary admiration.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>With exceptionally keen powers of observation and great finesse with a paintbrush, she recorded subtle nuances of colour, shape, and light 【that enlivened her paintings and attracted a wide audience】.</t>
+          <t>The theory sounds eccentric but once he starts to explain the detective work 【that went into his deduction】, the skepticism gives way to wary admiration.</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
     </row>
-    <row r="56" ht="76" customHeight="1">
+    <row r="56" ht="44" customHeight="1">
       <c r="A56" s="4" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3b668fa7a727</t>
+          <t>gi_v02_bb643b98ed2b</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C10 状语从句：识别与边界</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>This, however, cannot explain changes in pronunciation unless it can be shown that there is some systematic trend in the failures of imitation: if they are merely random deviations they will cancel one another out and there will be no net change in the language.</t>
+          <t>As the forest grew more dense, people probably used axes to clear patches of forest and make hunting easier.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>This, however, cannot explain changes in pronunciation unless it can be shown 【that there is some systematic trend in the failures of imitation】: if they are merely random deviations they will cancel one another out and there will be no net change in the language.</t>
+          <t>【As the forest grew more dense】, people probably used axes to clear patches of forest and make hunting easier.</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
     </row>
-    <row r="57" ht="60" customHeight="1">
+    <row r="57" ht="76" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_603bed69f245</t>
+          <t>gi_v02_d8913fb025b7</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C10 状语从句：识别与边界</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Deciphered from a band of coded text on parchment, the find provides insight into the community of people who wrote it and the 364-day calendar they would have used.</t>
+          <t>Though the young player had been doing well in the tournament, she began having difficulty regulating her breathing and heart rate during a match, which she later attributed to "the accumulation of the excitement and the buzz."</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Deciphered from a band of coded text on parchment, the find provides insight into the community of people 【who wrote it】 and the 364-day calendar they would have used.</t>
+          <t>【Though the young player had been doing well in the tournament】, she began having difficulty regulating her breathing and heart rate during a match, which she later attributed to "the accumulation of the excitement and the buzz."</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr"/>
@@ -4725,96 +4725,96 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_06f143584879</t>
+          <t>gi_v02_699e5df3d086</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>G-C04 定语从句：边界与先行词</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>划出句中的定语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Noise usually means unwanted sounds which interfere with genuine information.</t>
+          <t>Managers must be sure, therefore, that employees feel confident that their efforts can lead to performance goals.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Noise usually means unwanted sounds 【which interfere with genuine information】.</t>
+          <t>Managers must be sure, therefore, 【that employees feel confident that their efforts can lead to performance goals】.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
     </row>
-    <row r="59" ht="44" customHeight="1">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d3f5311a9963</t>
+          <t>gi_v02_5d2bf0b4d94a</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>G-C02 并列分句</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>划出句中的并列分句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>High achievers will do best when the job provides moderately challenging goals and where there is independence and feedback.</t>
+          <t>He believes the extra woodland will also benefit the farms by reducing their water usage through a lowering of evaporation and providing a refuge for bio-control insects.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>High achievers will do best when the job provides moderately challenging goals and 【where there is independence and feedback】.</t>
+          <t>He believes 【the extra woodland will also benefit the farms】 by reducing their water usage through a lowering of evaporation and providing a refuge for bio-control insects.</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
-    <row r="60" ht="76" customHeight="1">
+    <row r="60" ht="44" customHeight="1">
       <c r="A60" s="4" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_d24cb5852ce6</t>
+          <t>gi_v02_94e0647c0201</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>G-C10 状语从句：识别与边界</t>
+          <t>G-C08 名词性从句及其成分</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Ericsson's memory research is particularly interesting because random students, trained in memory techniques for the study, went on to outperform others thought to have innately superior memories - those who you might call gifted.</t>
+          <t>However, one should not assume subtitling is easier than dubbing.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Ericsson's memory research is particularly interesting 【because random students, trained in memory techniques for the study, went on to outperform others thought to have innately superior memories - those who you might call gifted】.</t>
+          <t>However, one should not assume 【subtitling is easier than dubbing】.</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr"/>
@@ -4827,28 +4827,28 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_17bc887ea8e8</t>
+          <t>gi_v02_2bb470826ea8</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>G-C08 名词性从句及其成分</t>
+          <t>G-C10 状语从句：识别与边界</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>划出句中的名词性从句（从第一个词划到最后一个词）。</t>
+          <t>划出句中的状语从句（从第一个词划到最后一个词）。</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>The most surprising thing of all is that no ecologists have thought to conduct proper research into this human-made rainforest ecosystem.</t>
+          <t>It was once assumed that improvements in telecommunications would lead to more dispersal in the population as people were no longer forced into cities.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>The most surprising thing of all is 【that no ecologists have thought to conduct proper research into this human-made rainforest ecosystem】.</t>
+          <t>It was once assumed that improvements in telecommunications would lead to more dispersal in the population 【as people were no longer forced into cities】.</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_38d91e97eb30</t>
+          <t>gi_v02_96380f59ea79</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>The use of prefabricated elements, metal frames, concrete cladding and the absence of decoration – 【all of which had been embraced by Modernists abroad and viewed with suspicion by the British】 - were adopted to varying degrees for housing developments and schools.</t>
+          <t>He was also helped by six assistants, two of whom died 【whilst the Dictionary was still in preparation】.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>状语从句</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr"/>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d2906c6416e2</t>
+          <t>gi_v02_347d1d9f3ce6</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>That means companies, governments and other players in space are collaborating in new ways 【to avoid a shared threat】.</t>
+          <t>And although many candidate countries inherited a transport system which encourages rail, the distribution between modes has tipped sharply in favour of road transport 【since the 1990s】.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_5981761cf2aa</t>
+          <t>gi_v02_2435d813f6ea</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Deciphered from a band of coded text on parchment, the find provides insight into the community of people 【who wrote it】 and the 364-day calendar they would have used.</t>
+          <t>The catchphrase 'Trade Not Aid' was used by church groups and trade unions – early supporters of fair trade – who also considered 【that international aid was either a pittance or a covert form of subjugation】.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>名词性从句</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_a2fffced3259</t>
+          <t>gi_v02_2c31cb3d2294</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Zambia and Mozambique have both welcomed exiled white Zimbabwean farmers, 【whose skills are already boosting local agriculture】.</t>
+          <t>In the years that have followed, more and more rail systems have been put in, 【dramatically changing the nature of the city】.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_5ce184580b40</t>
+          <t>gi_v02_6f3a60544c08</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>As with wolves, bears, beavers, boar, bison, moose and many other species, the lynx has been able to spread as farming has left the hills and people discover 【that it is more lucrative to protect charismatic wildlife than to hunt it】, as tourists will pay for the chance to see it.</t>
+          <t>Folklorists believe that what happens in a story is more central to the story than the characters in it – that visiting a relative, 【only to be met by a scary animal in disguise】, is more fundamental than whether the visitor is a little girl or three siblings, or the animal is a tiger instead of a wolf.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_f38bc28a9f82</t>
+          <t>gi_v02_e481179754df</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>This jerk meant 【that kites could lift huge weights】, Gharib realised.</t>
+          <t>It recorded on the 2005-15 Yokohama Strategy Action Plan 【that participant countries and agencies should work over the next 10 years to reduce vulnerability to natural disasters】.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a009dc639adb</t>
+          <t>gi_v02_a4fbcd5fe869</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>And the view of repetitively boring lessons and learning the facts by heart, 【which is sometimes quoted in relation to Japanese classes】, may be unfair and unjustified.</t>
+          <t>No mechanical means of stripping cork bark has been invented, 【so the job is done by teams of highly skilled workers】.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>并列分句</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_6d932d7537a6</t>
+          <t>gi_v02_eb1756372a95</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>【In its most recent variant (1980)】, it consists of the reading of vocabulary and text while the class is listening to music.</t>
+          <t>'The principle of social proof is so pervasive 【that we don't even recognise it】,' says Cialdini.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>状语从句</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_467013d4ecbd</t>
+          <t>gi_v02_5199cc970432</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Microbes 【that sit contentedly in the human gut】 (where there are more microbes than there are stars in the galaxy) can become deadly if they find their way into the bloodstream.</t>
+          <t>Warships were built 【to be lightweight and very speedy】.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_9729aeb6025b</t>
+          <t>gi_v02_9a4731111305</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>The real adventure didn't begin, however, until their Lapita descendants sailed out of sight of land, 【with empty horizons on every side】.</t>
+          <t>The aim was to use a helicopter 【to move 300 of the breeding centre's tortoises to various locations close to Sierra Negra】.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_d4752091969b</t>
+          <t>gi_v02_3ea10c6909b4</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Carefully fostered class identity makes pupils keen to help each other - anyway, it is in their interests 【since the class progresses together】.</t>
+          <t>Research 【surfacing in many parts of the world】 now cautions that each of these essential 'deep reading' processes may be under threat as we move into digital-based modes of reading.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>状语从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_1041d82669fd</t>
+          <t>gi_v02_84cf4bc752b5</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>At the extreme, they can jeopardize a company by ceding to rivals the opportunity 【to transform the industry】.</t>
+          <t>Even now, silk 【processed in the province of Como in northern Italy】 enjoys an esteemed reputation.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_e3a2b6438b62</t>
+          <t>gi_v02_f32c1de8ac0f</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>He recalls how the scheme succeeded in attracting a great deal of attention—particularly 【when it came to publicising Provo's aims】—but struggled to get off the ground.</t>
+          <t>Although cellulose breaks down less easily than sugars and starches and 【thus requires a complex series of enzyme-driven chemical reactions】, its use opens the industry to nonfood plant feedstocks such as agricultural wastes, wood chips, and switchgrass.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>状语从句</t>
+          <t>并列分句</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e45ded4898ab</t>
+          <t>gi_v02_32f077f03d28</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>The two sides finally faced one another at Worcester 【in the west of England】 in 1651.</t>
+          <t>However, laws in certain parts of Florida now limit boat speeds during winter, 【allowing slow-moving manatees more time to respond】.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_49251d88ac1f</t>
+          <t>gi_v02_e6d76bbac6ac</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>It takes time, effort and money 【to organise, build trust and to experiment】.</t>
+          <t>Some recent wildfires are among the biggest ever in California in terms of acreage burned, 【according to state figures and news reports】.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_1b14251d9518</t>
+          <t>gi_v02_4fb7cd85e71f</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>As Venus was closer to the Earth, its parallax angle would be larger, and Halley worked out 【that by using Venus it would be possible to measure the Sun's distance to 1 part in 500】.</t>
+          <t>However, 【for Schimmelpennink and for bike-sharing schemes in general】, this was just the beginning.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_57aafaa09304</t>
+          <t>gi_v02_908295adc727</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>【If participation is inconsistent with the culture】, however, goals should be assigned.</t>
+          <t>The lynx presents no threat to human beings: there is no known instance 【of one preying on people】.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>状语从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_3006e6bdb2cc</t>
+          <t>gi_v02_4e901de3db77</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The purpose of this paper is to share some of the lessons 【S.K.I. and our partners have learned】.</t>
+          <t>Identification of harmful effects at this stage, on occasion, has led to withdrawal of a drug from the market; for example, as was the case with cerivastin, a cholesterol-lowering drug, which was later found to have an adverse effect on muscle reaction 【which, on occasion, had fatal consequences】.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_8545a3d8756f</t>
+          <t>gi_v02_327370fa2754</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Thus many temperate-zone birds use the increasing day lengths in spring as a cue 【to begin the nesting cycle】, because this is a point when adequate food resources will be assured.</t>
+          <t>This is surprising 【considering the high level of media coverage on this issue】.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_1e22aabd681d</t>
+          <t>gi_v02_666203b2d822</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Many observers say deeper cuts are needed and developing nations, 【which have large and growing populations】, will one day have to join in.</t>
+          <t>The regional road was in such bad shape 【that access to the main towns was impossible for about three months of the year】.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>状语从句</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_24985496fcec</t>
+          <t>gi_v02_d8f2727655ab</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>The trend towards imposing prison sentences on offenders in the UK is made to seem all the more harsh 【since the Dutch Justice Ministry is actively in the process of systematically closing down prisons】.</t>
+          <t>Instead, the line used specially designed locomotives that were fitted with water tanks 【in which steam could be condensed】.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>状语从句</t>
+          <t>定语从句</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_6237fb12eac4</t>
+          <t>gi_v02_e47bfebe43d0</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Other parapsychologists believe 【the field is on the brink of collapse】, having tried to produce definitive scientific proof and failed.</t>
+          <t>'Anyone 【with the right skills】 could go to their lab and do this.'</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_f3dc89252a4b</t>
+          <t>gi_v02_505bf4510a1c</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>The chosen route ran beneath existing main roads to minimise the expense 【of demolishing buildings】.</t>
+          <t>We now have hundreds of tree-ring records from throughout the northern hemisphere, and many from south of the equator, too, 【amplified with a growing body of temperature data】 from ice cores drilled in Antarctica, Greenland, the Peruvian Andes, and other locations.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_400674320aa8</t>
+          <t>gi_v02_e9692521fdf7</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>There are plenty of places around the globe where people have no access to heavy machinery, but 【do know how to deal with wind, sailing and basic mechanical principles】.</t>
+          <t>Only by arming themselves with an understanding of why butterfly numbers are down can conservationists hope 【to halt or reverse the decline】.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>并列分句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_33301bbb1565</t>
+          <t>gi_v02_615593444d4a</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>The team found 【that participants who had sniffed oxytocin via a nasal spray beforehand invested more money than those who received a placebo instead】.</t>
+          <t>It is worth noting that 【contrary to popular perception】, rowers were not slaves but mostly Roman citizens enrolled in the military.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_6e9bd6f48fac</t>
+          <t>gi_v02_41cba4f2f00d</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>The Asian nations proved and are still proving 【that this is not the case】.</t>
+          <t>He finds that changes in land values predict future building height, but 【the reverse is not true】.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>并列分句</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_98634b70aa2a</t>
+          <t>gi_v02_b0351b676d56</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Epigenetic processes are chemical reactions 【tied to neither nature nor nurture】 but representing what researchers have called a 'third component'.</t>
+          <t>For example, the 1.4-kilometer Çevlik tunnel in Turkey, built 【to divert the floodwater threatening the harbor of the ancient city of Seleuceia Pieria】, had inscriptions on the entrance, still visible today, that also indicate that the tunnel was started in 69 CE and was completed in 81 CE.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_216edb07b2d2</t>
+          <t>gi_v02_137db7921e4a</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>It sounds paradoxical, because the idea behind this hypothesis is that the red pigment is made in autumn leaves to protect chlorophyll, the light-absorbing chemical, 【from too much light】.</t>
+          <t>Earl Miller, an expert at the Massachusetts Institute of Technology, studied the prefrontal cortex, 【which controls the brain while a person is multitasking】.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>定语从句</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_dfe014738eb2</t>
+          <t>gi_v02_a31525e7cc0d</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>The overkill model emerged in the 1960s, 【when it was put forth by Paul S. Martin of the University of Arizona】.</t>
+          <t>It simply wasn't going to work 【as something for the community】.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_26d01ad2b947</t>
+          <t>gi_v02_0af0417ae31e</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>It seems schools may not be providing an opportunity 【for children to re-express their ideas】 and so have them tested and refined by teachers and their peers.</t>
+          <t>A test 【that is more abstract, or more quantitative】, would provide a more controlled study of how cognitive processing works for different groups of people.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>定语从句</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_dcc9d238a33e</t>
+          <t>gi_v02_08e4bd4c9c7b</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>More immediately, conservationists can arm themselves with all this knowledge to spot the warning signs of species 【that may be at risk】.</t>
+          <t>As the ice has vanished, it has been giving up the treasures 【it has preserved in cold storage for the last 6,000 years】 – items such as ancient arrows and skis from Viking Age* traders.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_876cc5bcf891</t>
+          <t>gi_v02_63cbec77e780</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Is this a sign 【that butterflies are well equipped to cope with climate change, and readily adjust to new temperatures】?</t>
+          <t>In the role of cacher, not only nutcracker but also the less specialized jay performed above chance; 【more surprisingly, however, jay observers were as successful as jay cachers】 whereas nutcracker observers did no better than chance.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>并列分句</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3fc8a9514757</t>
+          <t>gi_v02_cee0bd785979</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bats comprise roughly one-fifth of all mammal species in Madagascar and thirty-six recorded bat species are native to the island, 【making it one of the most important regions for conservation of this animal group anywhere in the world】.</t>
+          <t>In the business world, much as in life in general, there are challenges that need to be faced, problems that need solutions and decisions 【that need to be made and acted upon】.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>定语从句</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c9f6326ecf67</t>
+          <t>gi_v02_15a8fa375640</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>There were several reasons 【why original science continued to be written in Latin】.</t>
+          <t>Other days can be hectic, with numerous life-threatening incidents to attend to; 【they’ll enter burning homes】 to rescue trapped residents, and assist with medical emergencies.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>并列分句</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_98e2676d9282</t>
+          <t>gi_v02_9e75ebe8ab3e</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Judging by the bones which the researchers unearthed in the Kelo caves, people living there mainly hunted the Rothschild's cuscus, a possum-like creature 【that still lives on Obi today】.</t>
+          <t>Flexibility is left to the Local, Region/Zone, Chapter and National Special Olympics organisations for determining the eligibility of the participants because of the variety of situations and needs 【that exist in the many localities】 where Special Olympics programmes have been and will be instituted.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e06afc229131</t>
+          <t>gi_v02_56a835cb8b30</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>However, some say that the real reason 【that parents fork out the cash】 is prejudice: they don't want their little kids mixing with the "workers", or picking up an undesirable accent.</t>
+          <t>It is particularly valuable in regions 【where natural groundwater reserves have been polluted】, or where seawater is the only water source available.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_8e10c80c6e50</t>
+          <t>gi_v02_0c40bcd704f9</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>As MIT scholar Sherry Turkle has written, we do not err as a society 【when we innovate】 but when we ignore what we disrupt or diminish while innovating.</t>
+          <t>Governments and authorities at every level have to formulate and execute plans 【for implementing the political, economic, and technological measures】 that can ensure water security now and in the coming decades.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>状语从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_adda47427dbc</t>
+          <t>gi_v02_adec67e113f1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Clan members are generally kinsfolk, 【related by descent or marriage】.</t>
+          <t>This growing concern about intellectual property rights was a feature of the period - it reflected both the humanist notion of the individual, rational scientist 【who invents and discovers through private intellectual labour】, and the growing connection between original science and commercial exploitation.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>定语从句</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3e1ba6483ce8</t>
+          <t>gi_v02_6d932d7537a6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Sessions involve encouragement of an individual 【to view themselves and their relationships in a more positive manner】, with the intention of helping patients to replace negative thoughts with a more positive outlook.</t>
+          <t>【In its most recent variant (1980)】, it consists of the reading of vocabulary and text while the class is listening to music.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5460edf88817</t>
+          <t>gi_v02_46579fba387b</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>And, in 【what would have been particularly pleasing to Perkin】, their current use is in the search for a vaccine against malaria.</t>
+          <t>This pronouncement 【by Richard Layard】, an economist and advocate of 'positive psychology', summarises the beliefs of many people today.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3c44c3c1c49a</t>
+          <t>gi_v02_8fc62aa7a722</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>This is in perfect harmony with the museum's function, 【since the approach is dedicated to seeking out and conserving 'authentic', 'original' readings of the exhibits】.</t>
+          <t>Bernstein predicts 'an avalanche of interest and support' 【if all goes well】.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5894e313fb97</t>
+          <t>gi_v02_5cd8e7a91771</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>If a woman has high blood-sugar levels 【while she's pregnant】, her children are more likely to be overweight or obese, according to a study of almost 10,000 mother-child pairs.</t>
+          <t>The creatures 【that particularly interest us】 are the many insects that secrete powerful poison for subduing prey and keeping it fresh for future consumption.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>状语从句</t>
+          <t>定语从句</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_033a8646d676</t>
+          <t>gi_v02_adedcff2b525</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Before the written word could be used to record history, people memorised it 【in songs】, says Leon James, a psychologist at the University of Hawaii.</t>
+          <t>Even today, people 【who identify as modern druids】 continue to gather at Stonehenge for the summer solstice.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>定语从句</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_1def3027d630</t>
+          <t>gi_v02_3a1d6d5fdede</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>In addition, trees with many cavities are extremely important habitats 【for insect predators like woodpeckers, bats and small mammals】.</t>
+          <t>Inspection technology allows more than 100 million measurements a second to be made across the ribbon, 【locating flaws the unaided eye would be unable to see】.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_886a5413b9d3</t>
+          <t>gi_v02_bcaafeef338e</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Video games are goal-driven experiences, says Gee, 【which are fundamental to learning】.</t>
+          <t>In any event, 【whether or not the reason is the energy expense】, it seems to be the case that, with the possible exception of some weird deep-sea fish, no animal apart from man uses manufactured light to find its way about.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>状语从句</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_9212c9016c37</t>
+          <t>gi_v02_8117d2e107e7</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Many schools and hospitals use wood boiler systems to heat and power their facilities, 【many homes are primarily heated with wood】, and some coal plants incorporate wood into their coal streams to produce electricity.</t>
+          <t>Venter has found 【that this may not be the case】.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>并列分句</t>
+          <t>名词性从句</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_86cda2dbd5ee</t>
+          <t>gi_v02_e954c4dfdc04</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Positive psychologists have identified 24 qualities we admire, 【such as loyalty and kindness】, and are studying them to find out why they come so naturally to some people.</t>
+          <t>This generated huge public interest and 【the bridge became known as London's "wobbly bridge. "】</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>并列分句</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_3f9ebd10b48d</t>
+          <t>gi_v02_1869f6d7d7a3</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>We don't always have control over some of those social factors that can make us look younger, 【but there are other steps we can take to try to stop the ravages of age】.</t>
+          <t>They observed 【that the probe had bounced after touchdown】 and carefully photographed the impressions made by its footpads.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>状语从句</t>
+          <t>名词性从句</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_5db5cba1fe1e</t>
+          <t>gi_v02_d0ac48676de4</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Having survived there for centuries, they believe 【their wealth of traditional knowledge is vital to the task】.</t>
+          <t>Much of the ingenuity present in 19th-century hospital and building design was driven by a panicked public 【clamouring for buildings】 that could protect against what was thought to be the lethal threat of miasmas - toxic air that spread disease.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_f7099a616de0</t>
+          <t>gi_v02_0c6f0bbb2110</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>They discovered that pregnant bears were able to increase the density of their bones 【before they started to build their dens】.</t>
+          <t>All of them offer the opportunity 【to acquire skills and knowledge】 that are useful throughout life.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>状语从句</t>
+          <t>不是从句（短语或非谓语）</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_7b70b5004d62</t>
+          <t>gi_v02_3f15527dba1b</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>He uses data 【to assess the viability of these two explanations】 and finds that supply and demand factors explain much of the development of the 1920s; though it enabled the boom, cheap credit was not, he argues, the primary cause.</t>
+          <t>The situation remained unchanged 【for thousands of years】.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_422638cd6b12</t>
+          <t>gi_v02_23faa8df3e9d</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Leslie argues 【that, before 18 months, children treat the world in a literal way and rarely demonstrate pretence】.</t>
+          <t>Firstly, there are so many insects 【that, without some manner of targeted approach, investigating this huge variety of species is a daunting task】.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>名词性从句</t>
+          <t>状语从句</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_1b518249e47b</t>
+          <t>gi_v02_5fae1270d27d</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>By understanding these constraints, we begin to understand 【why some people march to a different drumbeat】.</t>
+          <t>But he insists 【that cases are few and far between】.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_615da3330ca4</t>
+          <t>gi_v02_216edb07b2d2</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>In one well-known test, women and men were able to distinguish by smell alone clothing 【worn by their marriage partners】 from similar clothing worn by other people.</t>
+          <t>It sounds paradoxical, because the idea behind this hypothesis is that the red pigment is made in autumn leaves to protect chlorophyll, the light-absorbing chemical, 【from too much light】.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_6d0ed45cdb4f</t>
+          <t>gi_v02_4b3534a57b42</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>In conditions of good visibility, seamen in the Mediterranean often had the mainland or islands in sight, 【which greatly facilitated navigation】.</t>
+          <t>His harvest was as good as the harvests of farmers that were using pesticides, and he earned much more 【because he did not spend a single rupee on pesticides】.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>定语从句</t>
+          <t>状语从句</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e7f3c938664b</t>
+          <t>gi_v02_ab2f62ff2431</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>He later told me, "This is part of a movement 【to use algorithms to take the hard choices of living out of life】."</t>
+          <t>【Merely restricting tourism】 cannot be the solution to the imbalance, because people's desire to see new places will not just disappear.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_da3b230eb9a6</t>
+          <t>gi_v02_b29ffd960380</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>【To reach an exceptionally high standard in any area】, very able children need the means to learn, which includes material to work with and focused challenging tuition – and the encouragement to follow their dream.</t>
+          <t>Legend has it 【that it was Lei Tzu, wife of the Yellow Emperor, ruler of China in about 3000 BC, who discovered silkworms】.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>名词性从句</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr"/>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_10b49651151c</t>
+          <t>gi_v02_bf37503869ff</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>The team's earlier research suggested that the northernmost islands in the group, known as the Wallacean islands, 【including Obi】, would have offered the easiest migration route.</t>
+          <t>Recognising the importance of play is not new: over two millennia ago, the Greek philosopher Plato extolled its virtues as a means of developing skills for adult life, and 【ideas about play-based learning have been developing since the 19th century】.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>并列分句</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_35412c04b4ac</t>
+          <t>gi_v02_ba2e4478e45e</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>He has already set up a huarango festival 【to reinstate a sense of pride in their eco-heritage】, and has helped local schoolchildren plant thousands of trees.</t>
+          <t>A random group of volunteers then listened to an equal number of dominant and submissive laughs 【from both the high- and low-status individuals】, and were asked to estimate the social status of the laugher.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_664c7e93cc1a</t>
+          <t>gi_v02_2237002518d2</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>They were also pioneers who carried with them everything they would need 【to build new lives】 - their livestock, taro seedlings and stone tools.</t>
+          <t>They may have signed an online petition against road pricing, but 【ministers are determined】 to push ahead with plans to make it more expensive to drive.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>不是从句（短语或非谓语）</t>
+          <t>并列分句</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_4f610b65dea0</t>
+          <t>gi_v02_a2e7cd7de33f</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>【When you watch a programme filmed in the HD format】, you will see a much sharper, clearer and more vibrant image.</t>
+          <t>Merely restricting tourism cannot be the solution to the imbalance, 【because people's desire to see new places will not just disappear】.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_9086fe6715f0</t>
+          <t>gi_v02_c5e9798c8fc6</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>If I try to grab it, it will dart away, and I doubt whether I'll be able to catch it 【before it disappears into the numerous cracks and crevices of my old apartment】.</t>
+          <t>The rural markets in India cannot afford it, he says, 【until the prices are brought down】.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_77c7255ba1f4</t>
+          <t>gi_v02_a6a35d159970</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>"【If you are not depressed, not a smoker and not too skinny】, you are basically doing well," says Professor Kaare Christensen (married, three children, non-smoker), one of the report's authors.</t>
+          <t>Worse, 【though China took an early decision to invite foreign direct investment into manufacturing】, it has been reluctant to open up services.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>让步</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_2d4671825354</t>
+          <t>gi_v02_ded9f89785ab</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Since legislation requires subjects participating in such trials to be monitored for a considerable period of time 【so that side-effects and benefits can be assessed correctly】, a further eight years typically passes between the stage of a drug entering clinical trial and being approved for general use.</t>
+          <t>The preventative qualities of citrus fruit against scurvy were not truly recognised until 1800, 【though throughout the latter part of the 1700s, lemon juice was increasingly administered as a cure for sailors already afflicted】.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>让步</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a6a35d159970</t>
+          <t>gi_v02_9dad7cd3d23a</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Worse, 【though China took an early decision to invite foreign direct investment into manufacturing】, it has been reluctant to open up services.</t>
+          <t>【Although around two million farmers and workers produce fair-trade items】, this is a tiny number in relation to total global trade.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_f54f137863ba</t>
+          <t>gi_v02_5db7109faa85</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>For example, large storage jars (pithoi) would be needed to store commodities, 【whereas smaller containers would be used for transport】.</t>
+          <t>Unlike all previous studies, which only estimated how old the ants were, her work tracked the ants from the time the pupae became adults, 【so she knew their exact ages】.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>对比</t>
+          <t>结果</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_bd90f60ed66a</t>
+          <t>gi_v02_7e991b1420f5</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Eighty panes of its toughened glass shattered due to inclusions 【before experts were finally called in】.</t>
+          <t>【When latchkey children are functioning well】, we don't hear about them.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_3bee56937208</t>
+          <t>gi_v02_ba6d8a8abf7d</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>【Whereas in Hollywood the producer was the central figure】, in Tokyo the director chose the stories and hired the producer and actors.</t>
+          <t>Studies reveal that 【if a layer of air of about five centimetres could be held in place close to the skin】, it would provide the same insulation as does the impressively dense winter coat of the arctic fox.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>对比</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_71854780b204</t>
+          <t>gi_v02_253f3c0d8c9b</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>【Though many universities resisted the report】, today's world continues to change.</t>
+          <t>The psychologists reasoned that 【if the children knew what they usually looked like】, they would be surprised by the unusual red mark and would start touching it.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>让步</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_984088710272</t>
+          <t>gi_v02_b50f59f27c4a</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Tackling the problems of global warming is never easy in New Zealand, 【because records show the slow process of global warming may have a different impact on various regions】.</t>
+          <t>To think of geniuses and the gifted as having uniquely different brains is only reasonable 【if we accept that each human brain is uniquely different】.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_c77e651d1dfc</t>
+          <t>gi_v02_9625f95e5f95</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>They are more prone to experiencing regret after a purchase, and 【if their acquisition disappoints them】, their sense of well-being takes longer to recover.</t>
+          <t>For example, one argument is that 【if all packaging is white with black lettering】, people would have no choice but to read every box carefully.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_a13982d8ea6e</t>
+          <t>gi_v02_8611a4923477</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>【Although Perkin's fame was achieved and fortune assured by his first discovery】, the chemist continued his research.</t>
+          <t>So 【even if, on average, there is only one inclusion in 7 tonnes of glass】, if you experience one nickel sulphide failure in your building, that probably means you've got a problem in more than one pane.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_d15397d5a464</t>
+          <t>gi_v02_d70e966a24e3</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>【Whereas most exercises are designed to build up strength or endurance】, plyometrics focuses on increasing power—the rate at which an athlete can expend energy.</t>
+          <t>【Since parrots lack lips】 (another reason it was difficult for Alex to pronounce some sounds, such as ba), the words seemed to come from the air around him, as if a ventriloquist were speaking.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>对比</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e3a86a2e4e22</t>
+          <t>gi_v02_70cfb75a06fe</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Fortunately more schools are now saying: 'There is not much bullying here, but 【when it occurs】 we have a clear policy for dealing with it.'</t>
+          <t>So 【even if a punchline sounds silly】, the listener can see there is a clever semantic fit and that sudden mental 'Aha!' is the buzz that makes us laugh.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>让步</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_2d9f898b0de2</t>
+          <t>gi_v02_984088710272</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>【Although thousands of pirates died at the hands of Pompey's troops】, as a long-term solution to the problem, many more were offered land in fertile areas located far from the sea.</t>
+          <t>Tackling the problems of global warming is never easy in New Zealand, 【because records show the slow process of global warming may have a different impact on various regions】.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>让步</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_2136c6f3f6fb</t>
+          <t>gi_v02_7028667a6d36</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Employed by a studio as an assistant, a future director worked with senior figures, learned his craft, gained authority, 【until promoted to director with the power to select screenplays and performers】.</t>
+          <t>【If we accept this model】, it follows that streaming students with similar ZPDs would be an efficient and effective solution.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_66d529b93d1c</t>
+          <t>gi_v02_d13e99fc2d31</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>However, in ants there is no cultural transmission—everything must be encoded in the genes—【whereas in humans the opposite is true】.</t>
+          <t>【If an arctic fox or wolf is exposed to an air temperature of about minus ten degrees】, the temperature near the tips of the fur will match the air temperature, but at the surface of the skin it will be closer to thirty degrees.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>对比</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_ba6d8a8abf7d</t>
+          <t>gi_v02_c1b2dbf24024</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Studies reveal that 【if a layer of air of about five centimetres could be held in place close to the skin】, it would provide the same insulation as does the impressively dense winter coat of the arctic fox.</t>
+          <t>The idea of "infectobesity" came to him 20 years ago 【when he was a young doctor treating obesity in Bombay】.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_f1b1f5f66c56</t>
+          <t>gi_v02_0288e4606dbf</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>When dealers tried to punish NPM users by paying less for NPM cotton, the farmers united 【to form a marketing cooperative】 that found fairer prices elsewhere.</t>
+          <t>【Small tanks were still being used】, so batches were small and bottles were labelled and filled manually.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_b2eea6de571a</t>
+          <t>gi_v02_9288eedd32b4</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Gradually, layers are accumulated around the irritant 【until a lustrous natural pearl is formed】.</t>
+          <t>【Although the Government has poured millions into beefing up sport in the community】, there is less commitment to it as part of the crammed school curriculum.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>让步</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_815e7e5061e0</t>
+          <t>gi_v02_72f783bd7d1d</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Therefore, the lake will continue to grow 【until it reaches the glacier bed】.</t>
+          <t>Ericsson's memory research is particularly interesting 【because random students, trained in memory techniques for the study, went on to outperform others thought to have innately superior memories - those who you might call gifted】.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5e6bac6dd018</t>
+          <t>gi_v02_e1a0d044006b</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>【If the glass were kept hot enough】, it would flow over the molten tin until the top surface was also flat, horizontal and perfectly parallel to the bottom surface.</t>
+          <t>【If resistance to goals is expected】, the use of participation in goal-setting should increase acceptance.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_7028667a6d36</t>
+          <t>gi_v02_e14a71c4a87c</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>【If we accept this model】, it follows that streaming students with similar ZPDs would be an efficient and effective solution.</t>
+          <t>【If you have to cook】, steaming will retain at least some of the vitamins and minerals.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_9cb56f5c1db8</t>
+          <t>gi_v02_4b0291e7e23c</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>It was once believed, for example, that 【if a language had syllables[1] that begin with a vowel and end with a consonant (VC)】, it would also have syllables that begin with a consonant and end with a vowel (CV).</t>
+          <t>Why wait 【until you are forced off the road by costly charges】?</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_edca1987db7f</t>
+          <t>gi_v02_6b66d8e15d78</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>If the buyer wants detail, the seller provides it, 【if they are more interested in the feel of the product】, the seller will focus on this.</t>
+          <t>"Meditation and yoga enable you to shift the way that your brain reacts, so 【if you get proficient at it】 you're in control."</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4b1bd732d127</t>
+          <t>gi_v02_bb0bdfe21306</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>【As he looks to make the project self-sustainable】, he recognises that it is only urban markets - which have also shown an avid interest in LED lighting - that can pay.</t>
+          <t>Urban renewal areas are often very attractive 【since house and rental prices in such places are low right now but can be expected to rise in the not too distant future】.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_cfba8980f839</t>
+          <t>gi_v02_a1db38f71729</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>【When he saw how well the game held Sam's attention】, he wondered what sort of beast a more mature video game might be.</t>
+          <t>"【If I happen to miss a birthday or anniversary】, I know things are out of control."</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4fc14a204523</t>
+          <t>gi_v02_eee53ce7e2b7</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>【If ten times more palm oil can be produced from a patch of land than any competing oil】, then ten times more land would need to be cleared in order to produce the same volume of oil from that competitor.</t>
+          <t>For example, 【if a business school wanted a larger presence of employees at top financial firms】, this money may be better spent on a career center which focuses on building the skills of students, rather than paying for more high-level research to be done through the effort of faculty.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3cfba0eafd9a</t>
+          <t>gi_v02_6af9b8617c09</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>In fact, research shows that, 【when innovating】, the best approach is to create an environment devoid of structure and hierarchy and enable everyone involved to engage as one organic group.</t>
+          <t>And with the cash, health, and energy that returned 【when they stopped poisoning themselves with pesticides】, the villagers were inspired to start more community and business projects.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4eecbb855617</t>
+          <t>gi_v02_8b11cffee970</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Instead, communities in fragile environments must achieve greater control over tourism ventures in their regions, 【in order to balance their needs and aspirations with the demands of tourism】.</t>
+          <t>But Byers points out that the benefits of increased exercise disappear rapidly 【after training stops】, so any improvement in endurance resulting from juvenile play would be lost by adulthood.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a30efa237bc6</t>
+          <t>gi_v02_a7d0d63baf62</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Over the next two decades she made almost annual trips to New Mexico, staying up to six months there, painting in relative solitude, then returning to New York each winter 【to exhibit the new work at Stieglitz’s gallery】.</t>
+          <t>By the mid-1960s, the situation took an alarming turn with the outbreak of four more new pests, necessitating pesticide spraying to such an extent 【that 50% of the financial outlay on cotton production was accounted for by pesticides】.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>结果</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_70dedf50798f</t>
+          <t>gi_v02_c7aeff5291a6</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Most importantly, he says, people are much easier to motivate 【if they themselves can be involved in designing and deciding activities】 – this level of consultation at the planning stage being much easier to achieve for an internal department than an external consultant.</t>
+          <t>Likewise, 【if the tree suffers from black knot disease】, its value for timber decreases, but to a woodworker interested in making bowls, it brings an opportunity for a unique and beautiful piece of art.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_607683963cba</t>
+          <t>gi_v02_2f1f52e7de2c</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>【When they compare themselves with others】, they get little pleasure from finding out that they did better and substantial dissatisfaction from finding out that they did worse.</t>
+          <t>The rural markets would be able to afford it, says Mr. Irvine-Halliday, 【if they had access to microcredit】.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_42812c67c57e</t>
+          <t>gi_v02_1a1d4a5755ad</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>【If the buyer cracks jokes】, the salespeople will respond in kind.</t>
+          <t>By the seventh century, the word teon had become interchangeable with the tachund or hund of the Anglo-Saxon language, 【and so 100 was denoted as hund teontig, or ten times ten】.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>结果</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_9c0abb7a724e</t>
+          <t>gi_v02_d1f93631029c</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>So 【whether they were actually used to build the pyramids or not】, it seems that kites may make sensible construction tools in the 21st century AD.</t>
+          <t>In the face of the escalating perils from indiscriminate applications of pesticides, a more effective and ecologically sound strategy of biological control, involving the selective use of natural enemies of the pest population, is fast gaining popularity—【though, as yet, it is a new field with limited potential】.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_f7c639d38957</t>
+          <t>gi_v02_3bdf276a4cd0</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>This clearly illustrates the need for supplementary measures 【if one wants to assist the rural poor】.</t>
+          <t>【When satisficers find an item that meets their standards】, they stop looking.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr"/>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_f2b37431a238</t>
+          <t>gi_v02_deb14d7127fe</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Groundcherries are already sold to a limited extent in the US but they are hard to produce 【because the plant has a sprawling growth habit and the small fruits fall off the branches when ripe】.</t>
+          <t>【If we are kind to one another】, it's usually because we have ulterior motives.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_cf4b08935df5</t>
+          <t>gi_v02_3ae0081e84fc</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>For example, 【if the job is running a small business or an autonomous unit within a larger business】, high achievers should be sought.</t>
+          <t>I have learnt cash management and the way of keeping money 【so we save for reinvestment】.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>结果</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_e14a71c4a87c</t>
+          <t>gi_v02_b19a15443770</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>【If you have to cook】, steaming will retain at least some of the vitamins and minerals.</t>
+          <t>【When primitive automobiles first began to appear in the 1800s】, their engines were based on steam power.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_25702fce0ff2</t>
+          <t>gi_v02_2a92467d0907</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>[…] Of course, 【if you're cutting down virgin forest】 it's terrible – that's what's happening in Indonesia and Malaysia, it's been allowed to get out of hand.</t>
+          <t>Thus many temperate-zone birds use the increasing day lengths in spring as a cue to begin the nesting cycle, 【because this is a point when adequate food resources will be assured】.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3cf8f61544f5</t>
+          <t>gi_v02_839c85588857</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>This is not to be presented in a way that the preferred activity is only allowed 【if a defiant child does the non-preferred activity】.</t>
+          <t>Even a modest force, 【if sustained over a long time】, would do.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d8c3250bfac2</t>
+          <t>gi_v02_e1766192dd70</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>As a teacher myself, I'd think my lesson would be going rather well 【if the discussion went as described above】.</t>
+          <t>Sundays are the last bastion of the weekend - you want to get as much as you can out of the day 【before you have to go back to work】.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_bdac1557c80c</t>
+          <t>gi_v02_86638c9670a3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>【When it comes time to recall】, Cooke takes a mental walk along his route and translates the images into cards.</t>
+          <t>But the different noise conditions had quite different after-effects 【when the subjects were required to proofread written material under conditions of no noise】.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_6d7cfefbd303</t>
+          <t>gi_v02_4991b37db229</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>For first-time investors, lenders usually demand bigger down payments 【because you haven't got a proven track record】.</t>
+          <t>And it is all the more remarkable 【because the underlying ethos of medieval architecture was 'fitness for purpose'】.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_ca22cccef988</t>
+          <t>gi_v02_92f982d127df</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>【Though it did not run well】, the Doble brothers went on to build a second and third prototype in the following years.</t>
+          <t>【When scientists say the country's snow pack and glaciers are melting at an alarming rate due to global warming】, the climate is putting another strain on the local places.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>让步</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_179d134c01d6</t>
+          <t>gi_v02_fea7f6988908</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>In another entry, he coined the term Indo-European 【to describe the family of languages】 spoken throughout most of Europe and northern India.</t>
+          <t>Though Pajama Sam is not an "educational game", it is replete with the types of problems psychologists study 【when they study thinking and learning】.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_6b66d8e15d78</t>
+          <t>gi_v02_881977d1ac95</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>"Meditation and yoga enable you to shift the way that your brain reacts, so 【if you get proficient at it】 you're in control."</t>
+          <t>This data is used 【to wring improvements out of athletes】.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>目的</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_66ba41b4db20</t>
+          <t>gi_v02_61166b02ca86</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>So, Brown researchers set out to test whether teachers could detect problems with attention and learning when children stayed up late - 【even if the teachers had no idea how much sleep their students actually got】.</t>
+          <t>【Although piracy in the Mediterranean is first recorded in ancient Egypt during the reign of Pharaoh Amenhotep III (c. 1390–1353 BCE)】, it is reasonable to assume it predated this powerful civilisation.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_4c972ce0bfc7</t>
+          <t>gi_v02_bda011edf0d9</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>"【If a person shifts from Navajo to English】, they lose something," Mufwene says.</t>
+          <t>Usually, scientists don't know exactly how disasters such as a tanker accidentally spilling its whole cargo of oil and polluting huge areas of the ocean will affect the environment 【until after they've happened】.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_abb79959ac89</t>
+          <t>gi_v02_ef5ad544cfd8</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>【When summer comes】, we go to barbecues at family or friends' houses.</t>
+          <t>I don't like shopping on a Sunday 【because every man and his dog is out】.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_0628b13312c2</t>
+          <t>gi_v02_b69b1a401528</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>He will not predict by how much, however: "Exactly what the limits are it's hard to say, but there will be increases even if only by hundredths of a second, 【as long as our training continues to improve】."</t>
+          <t>There is considerable debate over how we should react 【if we detect a signal from an alien civilization】.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4c9547e6979f</t>
+          <t>gi_v02_c507f787ce4e</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>The psychologists reasoned that if the children knew what they usually looked like, 【they would be surprised by the unusual red mark and would start touching it】.</t>
+          <t>In Norway, 【after an intervention campaign was introduced nationally】, an evaluation of forty-two schools suggested that, over a two-year period, bullying was halved.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>结果</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_81259412f14b</t>
+          <t>gi_v02_806aa1561597</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>‘【When I started this】,’ explains founder Elizabeth English, ‘climate change was not on the tip of everybody’s tongue, but this technology is becoming necessary in places that didn’t previously need it.’</t>
+          <t>'【If we could discharge clouds】, we might affect the weather,' he says.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr"/>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_6e9877a6a59b</t>
+          <t>gi_v02_3cfba0eafd9a</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Yet, even if America's trash output continues to rise as it has done in the past, 【and even if the American population doubles by 2100】, all the rubbish America produces through the entire 21st century will still take up only one-12,000th of the area of the entire United States.</t>
+          <t>In fact, research shows that, 【when innovating】, the best approach is to create an environment devoid of structure and hierarchy and enable everyone involved to engage as one organic group.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a352875d0799</t>
+          <t>gi_v02_5c9692ab4d21</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>【As most of the farmers were poor, illiterate, and without previous experience using agricultural chemicals】, they were forced to rely on local, small-scale agricultural dealers for advice.</t>
+          <t>For example, the fact that 【before we learn to speak】 we perceive the world as a place full of things causing actions (agents) and things having actions done to them (patients) explains why most languages deploy these grammatical categories.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr"/>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5dd1972e5262</t>
+          <t>gi_v02_3a77a91ecfaa</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Others are developing taxonomies of space debris – working on measuring properties such as the shape and size of an object, 【so that satellite operators know how much to worry about what's coming their way】.</t>
+          <t>Morris's influence grew from the production of furniture and textiles, 【until by the 1880s a generation of principled young architects was following his call for good, honest construction】.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr"/>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_c1043cb1e2e5</t>
+          <t>gi_v02_6f383864d854</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>This development is a response to market forces and, 【although museums and heritage sites have a special, rather distinct, role to fulfil】, they are also operating in a very competitive environment, where visitors make choices on how and where to spend their free time.</t>
+          <t>When fully developed, this system will enable him to build a biomechanical profile for coaches to use 【to help budding swimmers】.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>让步</t>
+          <t>目的</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr"/>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_b998c998da12</t>
+          <t>gi_v02_ae2733bdc2bb</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Veil Albert Kallio, a Finnish scientist, says that such an idea is impractical, 【because the force of the ice would ultimately snap the cables and rapidly release a large quantity of frozen ice into the sea】.</t>
+          <t>The main worry regarding misinformation is its potential to unduly influence attitudes and behavior, leading people to think and act differently than they would 【if they were correctly informed】, as suggested by the research teams of Stephan Lewandowsky of the University of Bristol and Elizabeth Marsh of Duke University, among others.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>条件</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr"/>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_74e62eeb6224</t>
+          <t>gi_v02_df815e1bc263</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>【If concrete is the only answer to the construction of new cities】, then carbon emissions will soar, aggravating global warming.</t>
+          <t>And 【because survival depended on access to resources—such as rivers, forests and animals—】there was bound to be conflict between rival groups, which led to the development of traits such as racism and warfare.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>条件</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr"/>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_7b3237dcc3c3</t>
+          <t>gi_v02_95e5ff5ea769</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Moulds had to be carefully designed 【so that the molten Bakelite would flow evenly and completely into the mould】.</t>
+          <t>【Though the project cost A$1.6 million (nearly £700,000)】, the alternative - re-cladding the entire building - would have cost ten times as much.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>让步</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr"/>
@@ -10270,13 +10270,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_af7bdcea6005</t>
+          <t>gi_v02_c59a580f8f7d</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10291,26 +10291,26 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>From 1819 he was superintendent of the Nautical Almanac and secretary to the Board of Longitude.</t>
+          <t>Recent experience in Didcot has demonstrated that large greenfield [1] developments cannot resource all the necessary infrastructure and low-cost housing requirements.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>From 1819 【he】 was superintendent of the Nautical Almanac and secretary to the Board of Longitude.</t>
+          <t>【Recent experience in Didcot】 has demonstrated that large greenfield [1] developments cannot resource all the necessary infrastructure and low-cost housing requirements.</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
     </row>
-    <row r="3" ht="44" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_3ff88ada5d14</t>
+          <t>gi_v02_41f4e53ce1a3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10325,13 +10325,13 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Older bilinguals enjoy improved memory relative to monolingual people, which can lead to real-world health benefits.</t>
+          <t>In the story of Little Red Riding Hood that European children are familiar with, a young girl on the way to see her grandmother meets a wolf and tells him where she is going.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>【Older bilinguals】 enjoy improved memory relative to monolingual people, which can lead to real-world health benefits.</t>
+          <t>In the story of Little Red Riding Hood that European children are familiar with, 【a young girl on the way to see her grandmother】 meets a wolf and tells him where she is going.</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr"/>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_7c6298f7489b</t>
+          <t>gi_v02_99ce32b92e45</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10359,26 +10359,26 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>In 1931, he held an exhibition at the Leicester Galleries in London.</t>
+          <t>This may be down to our brain's 'mirror neurons', which are known to mimic others' actions.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>In 1931, 【he】 held an exhibition at the Leicester Galleries in London.</t>
+          <t>【This】 may be down to our brain's 'mirror neurons', which are known to mimic others' actions.</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
     </row>
-    <row r="5" ht="76" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_60ae50507e39</t>
+          <t>gi_v02_dfac1ffa3f09</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -10393,13 +10393,13 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>While it is possible that much of our food will be grown in skyscrapers in future, most experts currently believe it is far more likely that we will simply use the space available on urban rooftops.</t>
+          <t>'The rock music's driving beat kind of aggravates people calling customer assistance with a problem,' said Kellaris.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>While it is possible that much of our food will be grown in skyscrapers in future, 【most experts】 currently believe it is far more likely that we will simply use the space available on urban rooftops.</t>
+          <t>'【The rock music's driving beat kind of】 aggravates people calling customer assistance with a problem,' said Kellaris.</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_2149cd18c9ed</t>
+          <t>gi_v02_9ff772f074be</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10427,26 +10427,26 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>The skin lacks a freshness and translucency.</t>
+          <t>Others, however, point out that the first weather stations in the far north date back just 50 years.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>【The skin】 lacks a freshness and translucency.</t>
+          <t>【Others, however】, point out that the first weather stations in the far north date back just 50 years.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
     </row>
-    <row r="7" ht="92" customHeight="1">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_467d8b66f18d</t>
+          <t>gi_v02_64d91909cd01</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10461,13 +10461,13 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Ogilvie, who discovered the inventories in the archives of two German communities 30 years ago, believes they may hold the answer to a conundrum that has long puzzled economists: the lack of evidence for a causal link between education and a country's economic growth.</t>
+          <t>He was the seventh child of Raymond Moore and his wife Mary Baker.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>【Ogilvie, who discovered the inventories in the archives of two German communities 30 years ago】, believes they may hold the answer to a conundrum that has long puzzled economists: the lack of evidence for a causal link between education and a country's economic growth.</t>
+          <t>【He】 was the seventh child of Raymond Moore and his wife Mary Baker.</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_fc041ba076f9</t>
+          <t>gi_v02_8b4a45a21ff6</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10495,13 +10495,13 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>So flooding is the obvious answer.</t>
+          <t>That means that they live life 'energetically'—more intensively, but not for as long.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>So 【flooding】 is the obvious answer.</t>
+          <t>【That】 means that they live life 'energetically'—more intensively, but not for as long.</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_74d818b03e17</t>
+          <t>gi_v02_c9de4dd25fd2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10529,26 +10529,26 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>The research on culture's effect on cognitive processing still goes on today, and while some criticisms exist of Bessett's early studies, the projects still provide valuable insight.</t>
+          <t>It could accelerate from zero to sixty miles per hour in just fifteen seconds, a feat described as 'remarkable acceleration' by Automobile magazine in 1914.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>【The research on culture's effect on cognitive processing】 still goes on today, and while some criticisms exist of Bessett's early studies, the projects still provide valuable insight.</t>
+          <t>【It】 could accelerate from zero to sixty miles per hour in just fifteen seconds, a feat described as 'remarkable acceleration' by Automobile magazine in 1914.</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="76" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_6ce2f810cff8</t>
+          <t>gi_v02_5d8b629bf172</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10563,13 +10563,13 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Experts generally agree that different options may succeed or fail depending upon the culture of the organisation in which they are implemented.</t>
+          <t>To find out the extent to which such disruption may claim people's daily time, an IBM Research team led by Jennifer Lai from Carnegie Mellon University studied ten managers, researchers and interns at the workplace.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>【Experts】 generally agree that different options may succeed or fail depending upon the culture of the organisation in which they are implemented.</t>
+          <t>To find out the extent to which such disruption may claim people's daily time, 【an IBM Research team led by Jennifer Lai from Carnegie Mellon University】 studied ten managers, researchers and interns at the workplace.</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_421048593079</t>
+          <t>gi_v02_7e7d655560a0</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10597,13 +10597,13 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Machines can already navigate, remember and search for items with an ability that far outstrips humans.</t>
+          <t>Without a shadow of a doubt, out of all European countries, the UK has adopted the most hardline approach to offenders.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>【Machines】 can already navigate, remember and search for items with an ability that far outstrips humans.</t>
+          <t>Without a shadow of a doubt, out of all European countries, 【the UK】 has adopted the most hardline approach to offenders.</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_100565f834de</t>
+          <t>gi_v02_d798a367ae4e</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10631,13 +10631,13 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>The fastest commercial sailing vessels of all time were clippers, three-masted ships built to transport goods around the world, although some also took passengers.</t>
+          <t>Although some of this can be attributed to a higher income, Manton believes it is mainly because educated people seek more medical attention.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>【The fastest commercial sailing vessels of all time】 were clippers, three-masted ships built to transport goods around the world, although some also took passengers.</t>
+          <t>Although some of this can be attributed to a higher income, 【Manton】 believes it is mainly because educated people seek more medical attention.</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d72a9636caa4</t>
+          <t>gi_v02_4cae7dda6c95</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10665,13 +10665,13 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>This is partly due to the great importance the Mediterranean held at this time, and partly due to its geography.</t>
+          <t>The researchers focused on how living environment and nationality might influence how people think.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>【This】 is partly due to the great importance the Mediterranean held at this time, and partly due to its geography.</t>
+          <t>【The researchers】 focused on how living environment and nationality might influence how people think.</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_af9989b44c61</t>
+          <t>gi_v02_247382d42a51</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10699,13 +10699,13 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>In 2004, physician-scientist Mauro Zappaterra began his PhD research at Harvard Medical School.</t>
+          <t>And a similar revelation is now dawning on hydrologists.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>In 2004, 【physician-scientist Mauro Zappaterra】 began his PhD research at Harvard Medical School.</t>
+          <t>And 【a similar revelation】 is now dawning on hydrologists.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c3ab78f0e4db</t>
+          <t>gi_v02_4222ac81c2f0</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10733,13 +10733,13 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Yet such a system has drawbacks.</t>
+          <t>One limitation is related to the way the museum presents its exhibits.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Yet 【such a system】 has drawbacks.</t>
+          <t>【One limitation】 is related to the way the museum presents its exhibits.</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_676da79b032b</t>
+          <t>gi_v02_965e662597b9</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10767,13 +10767,13 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>For instance, the tomato strains grown for supermarkets have lost much of their flavour.</t>
+          <t>Dubbing, although seemingly more accessible to movie watchers, comes with many disadvantages.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>For instance, 【the tomato strains grown for supermarkets】 have lost much of their flavour.</t>
+          <t>【Dubbing, although seemingly more accessible to movie watchers】, comes with many disadvantages.</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr"/>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_7b3c2117b022</t>
+          <t>gi_v02_0636e8cf2852</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10801,26 +10801,26 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>During the period known as the Industrial Revolution, new technologies helped make chocolate less costly to produce.</t>
+          <t>The weight of the building is supported entirely by twelve outer and four inner columns.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>During the period known as the Industrial Revolution, 【new technologies】 helped make chocolate less costly to produce.</t>
+          <t>【The weight of the building】 is supported entirely by twelve outer and four inner columns.</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="76" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_dad1c87b2367</t>
+          <t>gi_v02_93567a0471ac</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10835,13 +10835,13 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>"A better educated and less accepting public has become disillusioned with the experts in general and increasingly skeptical about science and empirically based knowledge," they said.</t>
+          <t>In the Coskata operation, a conventional gasification system will use heat to turn various feedstocks into a mixture of carbon monoxide and hydrogen called syngas, says Richard Tobey, vice president of Engineering and R&amp;D.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>"【A better educated and less accepting public】 has become disillusioned with the experts in general and increasingly skeptical about science and empirically based knowledge," they said.</t>
+          <t>In the Coskata operation, 【a conventional gasification system】 will use heat to turn various feedstocks into a mixture of carbon monoxide and hydrogen called syngas, says Richard Tobey, vice president of Engineering and R&amp;D.</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5fd1db6e554c</t>
+          <t>gi_v02_5f560fdf9ce8</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10869,26 +10869,26 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>"Bondi" or"Boondi" is an Aboriginal word meaning water breaking over rocks or the sound of breaking waves.</t>
+          <t>The Travel Planner offered suggested routes and public transport options between the chosen locations.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>"【Bondi" or"Boondi】" is an Aboriginal word meaning water breaking over rocks or the sound of breaking waves.</t>
+          <t>【The Travel Planner】 offered suggested routes and public transport options between the chosen locations.</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="44" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_9125fe9b12ce</t>
+          <t>gi_v02_f86937939abe</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -10903,13 +10903,13 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>This involves children's ability to understand that people can have different beliefs and representations of the world– a capacity that is shown by four years of age.</t>
+          <t>Speech is often unclear and ambiguous.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>【This】 involves children's ability to understand that people can have different beliefs and representations of the world– a capacity that is shown by four years of age.</t>
+          <t>【Speech】 is often unclear and ambiguous.</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_b585db4bfb7b</t>
+          <t>gi_v02_c3f19be1705a</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10937,26 +10937,26 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>For example, many species like hawthorn provide food for wildlife.</t>
+          <t>In the 1930s and 40s, this freedom of the director led to the production of some of Asia's finest films.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>For example, 【many species like hawthorn】 provide food for wildlife.</t>
+          <t>In the 1930s and 40s, 【this freedom of the director】 led to the production of some of Asia's finest films.</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
-    <row r="22" ht="44" customHeight="1">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_8f880873e568</t>
+          <t>gi_v02_fc4808ac7b18</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10971,13 +10971,13 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>And this, he believes, can ease the financial pressure on farmers to turn forest into fields.</t>
+          <t>The four-year pilot study included 380 families who were about to have their first child and who represented a cross-section of socio-economic status, age and family configurations.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>And 【this, he believes】, can ease the financial pressure on farmers to turn forest into fields.</t>
+          <t>【The four-year pilot study】 included 380 families who were about to have their first child and who represented a cross-section of socio-economic status, age and family configurations.</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5521bb9bcf3e</t>
+          <t>gi_v02_ce5cfb76cd00</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11005,26 +11005,26 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Lei Tzu found that she could wind this thread around her fingers.</t>
+          <t>To feed the people, even more land had to be cleared.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>【Lei Tzu】 found that she could wind this thread around her fingers.</t>
+          <t>To feed the people, 【even more land】 had to be cleared.</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="44" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_324f2a00ccdb</t>
+          <t>gi_v02_076fb1a308f4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -11039,26 +11039,26 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>By some estimate, the average American collects an annual 'sleep debt' of 500 hours - subtracting from an assumed norm of eight hours a night.</t>
+          <t>Moreover, people inadvertently have been sharing inaccurate information with one another for thousands of years.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>By some estimate, 【the average American】 collects an annual 'sleep debt' of 500 hours - subtracting from an assumed norm of eight hours a night.</t>
+          <t>Moreover, 【people】 inadvertently have been sharing inaccurate information with one another for thousands of years.</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="44" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5f73e8385910</t>
+          <t>gi_v02_46a92ce02130</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -11073,26 +11073,26 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Yet it left the magnificent five-storey pagoda at the Toji temple in nearby Kyoto unscathed, though it levelled a number of buildings in the neighbourhood.</t>
+          <t>Several processes - melting, refining, homogenising - take place simultaneously in the 2000 tonnes of molten glass in the furnace.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Yet 【it】 left the magnificent five-storey pagoda at the Toji temple in nearby Kyoto unscathed, though it levelled a number of buildings in the neighbourhood.</t>
+          <t>【Several processes - melting, refining, homogenising -】 take place simultaneously in the 2000 tonnes of molten glass in the furnace.</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
     </row>
-    <row r="26" ht="44" customHeight="1">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_19d9cc09d481</t>
+          <t>gi_v02_6937da01a330</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11107,26 +11107,26 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Their most famous hostage was none other than Julius Caesar, captured in 75 BCE.</t>
+          <t>In 1966, the U.S.F.S reported over 20,000 visitors to the Ancient Bristlecone Pine Forest, a figure which could exceed 40,000 today.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>【Their most famous hostage】 was none other than Julius Caesar, captured in 75 BCE.</t>
+          <t>In 1966, 【the U.S.F.S】 reported over 20,000 visitors to the Ancient Bristlecone Pine Forest, a figure which could exceed 40,000 today.</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
     </row>
-    <row r="27" ht="44" customHeight="1">
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_8563f8a87bf6</t>
+          <t>gi_v02_5a038360c3c3</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -11141,13 +11141,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Their careers depend on being seen in the right journals.</t>
+          <t>After three logging sales and a major fire in 1997, the researchers were also able to study the ecosystem's reaction to logging and disturbance.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>【Their careers】 depend on being seen in the right journals.</t>
+          <t>After three logging sales and a major fire in 1997, 【the researchers】 were also able to study the ecosystem's reaction to logging and disturbance.</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_3b31d567de6a</t>
+          <t>gi_v02_2bcdcea4edf7</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11175,13 +11175,13 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>They competed by building ever bigger figures.</t>
+          <t>But Kellaris' conclusions may hold some distressing news for companies.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>【They】 competed by building ever bigger figures.</t>
+          <t>But 【Kellaris' conclusions】 may hold some distressing news for companies.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c3f19be1705a</t>
+          <t>gi_v02_8339ad776ec0</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -11209,26 +11209,26 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>In the 1930s and 40s, this freedom of the director led to the production of some of Asia's finest films.</t>
+          <t>TSI Cuts can be tailored to one farmer's specific management goals for his or her land.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>In the 1930s and 40s, 【this freedom of the director】 led to the production of some of Asia's finest films.</t>
+          <t>【TSI Cuts】 can be tailored to one farmer's specific management goals for his or her land.</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="44" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a5c738060eec</t>
+          <t>gi_v02_1fe1c4dc0cb9</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -11243,13 +11243,13 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Centuries later the Greek physician Hippocrates recommended the bark of the willow tree as a remedy for the pains of childbirth and as a fever reducer.</t>
+          <t>• The involvement of the participants has been essential to the development of relevant programs.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Centuries later 【the Greek physician Hippocrates】 recommended the bark of the willow tree as a remedy for the pains of childbirth and as a fever reducer.</t>
+          <t>• 【The involvement of the participants】 has been essential to the development of relevant programs.</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_1fe1c4dc0cb9</t>
+          <t>gi_v02_caa504ef06d6</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -11277,26 +11277,26 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>• The involvement of the participants has been essential to the development of relevant programs.</t>
+          <t>State promises to provide more up-to-date engines, planes, and helicopters to fight fires have been fulfilled.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>• 【The involvement of the participants】 has been essential to the development of relevant programs.</t>
+          <t>【State promises to provide more up-to-date engines, planes, and helicopters to fight fires】 have been fulfilled.</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="44" customHeight="1">
       <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_b311a64ccd17</t>
+          <t>gi_v02_69b340df7e2b</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11311,13 +11311,13 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>But Salikoko Mufwene, who chairs the Linguistics department at the University of Chicago, argues that the deadliest weapon is not government policy but economic globalisation.</t>
+          <t>The result was a resin known as Novalak, which became soluble and malleable when heated.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>But 【Salikoko Mufwene, who chairs the Linguistics department at the University of Chicago】, argues that the deadliest weapon is not government policy but economic globalisation.</t>
+          <t>【The result】 was a resin known as Novalak, which became soluble and malleable when heated.</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_2f09af2714cf</t>
+          <t>gi_v02_66521ac38e26</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11345,13 +11345,13 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>In its earliest form, genius was concerned with the ability of the head of the family, the pater familias, to perpetuate himself.</t>
+          <t>Studies suggest that reducing deaths of one type of predator may have a negative impact on other species.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>In its earliest form, 【genius】 was concerned with the ability of the head of the family, the pater familias, to perpetuate himself.</t>
+          <t>【Studies】 suggest that reducing deaths of one type of predator may have a negative impact on other species.</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_08d18a89f1d9</t>
+          <t>gi_v02_d4a1f9badad5</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11379,13 +11379,13 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Soccer has Video Assistant Referees (for offside decisions, for example).</t>
+          <t>The RCA innovation exhibition this year revealed designs for a number of innovative objects.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>【Soccer】 has Video Assistant Referees (for offside decisions, for example).</t>
+          <t>【The RCA innovation exhibition this year】 revealed designs for a number of innovative objects.</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_aef7f4aae1d6</t>
+          <t>gi_v02_7c66e6614b58</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -11413,26 +11413,26 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>One of the worst examples of this is Waterfront Place, which was completed in 1990.</t>
+          <t>Now the future is unfolding before our eyes.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>【One of the worst examples of】 this is Waterfront Place, which was completed in 1990.</t>
+          <t>Now 【the future】 is unfolding before our eyes.</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
     </row>
-    <row r="36" ht="60" customHeight="1">
+    <row r="36" ht="44" customHeight="1">
       <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_d55f580ff433</t>
+          <t>gi_v02_e7613c9d1603</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11447,13 +11447,13 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>If the individual knows that he or she can control the noise, this seems to eliminate both its negative effects at the time and its after-effects.</t>
+          <t>Poor farmers, who cannot afford chemicals, have it even worse.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>If the individual knows that he or she can control the noise, 【this】 seems to eliminate both its negative effects at the time and its after-effects.</t>
+          <t>【Poor farmers, who cannot afford chemicals】, have it even worse.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr"/>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_af1fe35e8641</t>
+          <t>gi_v02_36d73b195963</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -11481,13 +11481,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>People who have these kinds of habits are called multi-taskers.</t>
+          <t>He clearly had curiosity, character and determination.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>【People who have these kinds of habits】 are called multi-taskers.</t>
+          <t>【He】 clearly had curiosity, character and determination.</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr"/>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_921ad7579256</t>
+          <t>gi_v02_162b19ab6ee3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11515,13 +11515,13 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>'Habits and morals change, but the things that scare us, and the fact that we seek out entertainment that's designed to scare us – those are constant,' he says.</t>
+          <t>The most surprising thing of all is that no ecologists have thought to conduct proper research into this human-made rainforest ecosystem.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>'【Habits and morals】 change, but the things that scare us, and the fact that we seek out entertainment that's designed to scare us – those are constant,' he says.</t>
+          <t>【The most】 surprising thing of all is that no ecologists have thought to conduct proper research into this human-made rainforest ecosystem.</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_0ce609c2a8aa</t>
+          <t>gi_v02_8211b54169f1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11549,26 +11549,26 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Many parents spend a lot of time, particularly in the early months, copying their infant's vocalizations and expressions.</t>
+          <t>This notion is induced by the bias in its representation in museums and heritage centers.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>【Many parents】 spend a lot of time, particularly in the early months, copying their infant's vocalizations and expressions.</t>
+          <t>【This notion】 is induced by the bias in its representation in museums and heritage centers.</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
     </row>
-    <row r="40" ht="92" customHeight="1">
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_6694490dbc12</t>
+          <t>gi_v02_cbba55dffd88</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -11583,26 +11583,26 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>As with wolves, bears, beavers, boar, bison, moose and many other species, the lynx has been able to spread as farming has left the hills and people discover that it is more lucrative to protect charismatic wildlife than to hunt it, as tourists will pay for the chance to see it.</t>
+          <t>The three most significant types of fragile environment in these respects, and also in terms of the proportion of the Earth's surface they cover, are deserts, mountains and Arctic areas.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>As with wolves, bears, beavers, boar, bison, moose and many other species, 【the lynx】 has been able to spread as farming has left the hills and people discover that it is more lucrative to protect charismatic wildlife than to hunt it, as tourists will pay for the chance to see it.</t>
+          <t>【The three most significant types of fragile environment in these respects, and also in terms of the proportion of the Earth's surface they cover】, are deserts, mountains and Arctic areas.</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
     </row>
-    <row r="41" ht="44" customHeight="1">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_8c7fae207929</t>
+          <t>gi_v02_2b5a4a192b62</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -11617,26 +11617,26 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Perkin went back to the drawing board.</t>
+          <t>This method required greater planning and advanced knowledge of surveying, mathematics and geometry as both ends of a tunnel had to meet correctly at the center of the mountain.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>【Perkin】 went back to the drawing board.</t>
+          <t>【This method】 required greater planning and advanced knowledge of surveying, mathematics and geometry as both ends of a tunnel had to meet correctly at the center of the mountain.</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
     </row>
-    <row r="42" ht="44" customHeight="1">
+    <row r="42" ht="76" customHeight="1">
       <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_e2e9b7cb4c61</t>
+          <t>gi_v02_4f03b3415bd0</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -11651,13 +11651,13 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>The unintentional consequence has been to halt the natural eradication of underbrush, now the primary fuel for megafires.</t>
+          <t>'In Manzalah Lagoon, for example, the increase in mercury, lead, copper and zinc coincided with the building of the High Dam at Aswan, the availability of cheap electricity, and the development of major power-based industries,' he says.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>【The unintentional consequence】 has been to halt the natural eradication of underbrush, now the primary fuel for megafires.</t>
+          <t>'In Manzalah Lagoon, for example, 【the increase in mercury, lead, copper and zinc】 coincided with the building of the High Dam at Aswan, the availability of cheap electricity, and the development of major power-based industries,' he says.</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_9e011da7982e</t>
+          <t>gi_v02_0d535f80e9e7</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -11685,13 +11685,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>They were simply machines, robots programmed to react to stimuli but lacking the ability to think or feel.</t>
+          <t>He too was puzzled by the picture that had sparked Clemmons's interest.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>【They】 were simply machines, robots programmed to react to stimuli but lacking the ability to think or feel.</t>
+          <t>【He too】 was puzzled by the picture that had sparked Clemmons's interest.</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_7bbf4162f249</t>
+          <t>gi_v02_432fe67071c6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11719,13 +11719,13 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Most researchers agree that AI peaked around 1985.</t>
+          <t>The bridge links the City of London near St Paul's Cathedral with the Tate Modern art gallery on Bankside.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>【Most researchers】 agree that AI peaked around 1985.</t>
+          <t>【The bridge】 links the City of London near St Paul's Cathedral with the Tate Modern art gallery on Bankside.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4652db129b94</t>
+          <t>gi_v02_d3cf1b78b70a</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11753,26 +11753,26 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Each activity has its own nutritional needs.</t>
+          <t>I sincerely believe that all species, however small and seemingly insignificant, have a right to exist for their own sake.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>【Each activity】 has its own nutritional needs.</t>
+          <t>【I】 sincerely believe that all species, however small and seemingly insignificant, have a right to exist for their own sake.</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
     </row>
-    <row r="46" ht="44" customHeight="1">
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_2aca84fdad98</t>
+          <t>gi_v02_c38e27157355</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -11787,26 +11787,26 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>The method of cutting these huge figures was simply to remove the overlying grass to reveal the gleaming white chalk below.</t>
+          <t>For the better part of a century, most biologists have been reluctant to use those words, mindful of a principle of evolution that says 'evolution cannot run backwards'.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>【The method of cutting these huge figures】 was simply to remove the overlying grass to reveal the gleaming white chalk below.</t>
+          <t>For the better part of a century, 【most biologists】 have been reluctant to use those words, mindful of a principle of evolution that says 'evolution cannot run backwards'.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
     </row>
-    <row r="47" ht="76" customHeight="1">
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e6e7977cff35</t>
+          <t>gi_v02_78ab9c0ccdf8</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -11821,13 +11821,13 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Trends—technological, economic, environmental, social, or political—that affect how people perceive the world around them and shape what they expect from products and services present firms with unique opportunities for growth.</t>
+          <t>Sensitivity to the possibility of change in social relations is also key, along with compromise or integration of different attitudes and beliefs.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>【Trends—technological, economic, environmental, social, or political—that affect how people perceive the world around them and shape what they expect from products and services】 present firms with unique opportunities for growth.</t>
+          <t>【Sensitivity to the possibility of change in social relations】 is also key, along with compromise or integration of different attitudes and beliefs.</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_0602e1fc29b6</t>
+          <t>gi_v02_946b1eeb1d51</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -11855,26 +11855,26 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>But during a threat state, cortisol inhibits the positive effect of adrenaline, resulting in tighter blood vessels, higher blood pressure, slower psychological responses, and a faster heart rate.</t>
+          <t>The deep sea contains more nickel, cobalt and rare earth metals than all land reserves combined, according to the US Geological Survey.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>But during a threat state, 【cortisol】 inhibits the positive effect of adrenaline, resulting in tighter blood vessels, higher blood pressure, slower psychological responses, and a faster heart rate.</t>
+          <t>【The deep sea】 contains more nickel, cobalt and rare earth metals than all land reserves combined, according to the US Geological Survey.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="44" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_2388649e8cda</t>
+          <t>gi_v02_79a3c9af39c6</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -11889,26 +11889,26 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Despite the extensive coverage in the popular media of the destruction of rainforests, little formal information is available about children's ideas in this area.</t>
+          <t>The king assured Akhenaten he was prepared to punish any of his subjects involved in piracy.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Despite the extensive coverage in the popular media of the destruction of rainforests, 【little formal information】 is available about children's ideas in this area.</t>
+          <t>【The king】 assured Akhenaten he was prepared to punish any of his subjects involved in piracy.</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
     </row>
-    <row r="50" ht="76" customHeight="1">
+    <row r="50" ht="44" customHeight="1">
       <c r="A50" s="4" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_49c0846f6d10</t>
+          <t>gi_v02_ff065adcbd51</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -11923,13 +11923,13 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>The only entire book of the Hebrew Bible preserved among the manuscripts from Qumran is Isaiah; this copy, dated to the first century BCE, is considered the earliest biblical manuscript still in existence.</t>
+          <t>And, perhaps lacking anything else to do, the sailors set to with a will.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>【The only entire book of the Hebrew Bible preserved among the manuscripts from Qumran】 is Isaiah; this copy, dated to the first century BCE, is considered the earliest biblical manuscript still in existence.</t>
+          <t>And, perhaps lacking anything else to do, 【the sailors】 set to with a will.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d432012fe04e</t>
+          <t>gi_v02_d50d57607bcb</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -11957,26 +11957,26 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Even less attention has been paid to children living on the street or in difficult circumstances.</t>
+          <t>In many cases, the architectural style of the building further reinforces that notion.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>【Even less attention】 has been paid to children living on the street or in difficult circumstances.</t>
+          <t>In many cases, 【the architectural style of the building】 further reinforces that notion.</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
     </row>
-    <row r="52" ht="76" customHeight="1">
+    <row r="52" ht="44" customHeight="1">
       <c r="A52" s="4" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_6efc553553c7</t>
+          <t>gi_v02_f53b2bcd4c9b</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -11991,26 +11991,26 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Much of the ingenuity present in 19th-century hospital and building design was driven by a panicked public clamouring for buildings that could protect against what was thought to be the lethal threat of miasmas - toxic air that spread disease.</t>
+          <t>The quality of this research is assessed by academic publications.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>【Much of the ingenuity present in 19th-century hospital and building design】 was driven by a panicked public clamouring for buildings that could protect against what was thought to be the lethal threat of miasmas - toxic air that spread disease.</t>
+          <t>【The quality of this research】 is assessed by academic publications.</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
     </row>
-    <row r="53" ht="44" customHeight="1">
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_8c49146c3934</t>
+          <t>gi_v02_a449d534b391</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -12025,26 +12025,26 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>The witch is depicted in Cutty Sark's figurehead—the carving of a woman typically at the front of old sailing ships.</t>
+          <t>In a similar study, Oshin Vartanian of Toronto University asked volunteers to compare original paintings with ones which he had altered by moving objects around within the frame.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>【The witch】 is depicted in Cutty Sark's figurehead—the carving of a woman typically at the front of old sailing ships.</t>
+          <t>In a similar study, 【Oshin Vartanian of Toronto University】 asked volunteers to compare original paintings with ones which he had altered by moving objects around within the frame.</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
     </row>
-    <row r="54" ht="44" customHeight="1">
+    <row r="54" ht="76" customHeight="1">
       <c r="A54" s="4" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_932c037a2d5b</t>
+          <t>gi_v02_02092521e6c8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -12059,13 +12059,13 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>The latter, inaugurated in 2009, has 8,844 photovoltaic panels producing up to 1.14 GWh of electricity annually.</t>
+          <t>The results of the study lend support to the World Bank's recommendation that education budgets in developing countries should be increased, not just to help their economies, but also to improve child health.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>【The latter, inaugurated in 2009】, has 8,844 photovoltaic panels producing up to 1.14 GWh of electricity annually.</t>
+          <t>【The results of the study】 lend support to the World Bank's recommendation that education budgets in developing countries should be increased, not just to help their economies, but also to improve child health.</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr"/>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_f0da90a84ff3</t>
+          <t>gi_v02_bf405cecd6ab</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12093,26 +12093,26 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>The primary tourist market in Phase 3 of the model consists mainly of interstate visitors.</t>
+          <t>The same rule applies in business.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>【The primary tourist market in Phase 3 of the model】 consists mainly of interstate visitors.</t>
+          <t>【The same rule】 applies in business.</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="44" customHeight="1">
       <c r="A56" s="4" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_c379d132b2d2</t>
+          <t>gi_v02_eb6bca624ff7</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -12127,26 +12127,26 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>We are reminded of this even before we view a collection by the presence of security guards, attendants, ropes and display cases to keep us away from the exhibits.</t>
+          <t>In recent times companies have slowly started to embrace this disorganisation.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>【We】 are reminded of this even before we view a collection by the presence of security guards, attendants, ropes and display cases to keep us away from the exhibits.</t>
+          <t>In recent times 【companies】 have slowly started to embrace this disorganisation.</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
     </row>
-    <row r="57" ht="44" customHeight="1">
+    <row r="57" ht="76" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_90cc882ddbfa</t>
+          <t>gi_v02_a09e88c0722b</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12161,26 +12161,26 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>A more radical strategy is 'combine and transcend'.</t>
+          <t>Another factor that may boost the prospects for AI in the near future is that investors are now looking for firms using clever technology, rather than just a clever business model, to differentiate themselves.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>【A more radical strategy】 is 'combine and transcend'.</t>
+          <t>【Another factor that may boost the prospects for AI in the near future】 is that investors are now looking for firms using clever technology, rather than just a clever business model, to differentiate themselves.</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
     </row>
-    <row r="58" ht="76" customHeight="1">
+    <row r="58" ht="44" customHeight="1">
       <c r="A58" s="4" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_63ffca5c43ea</t>
+          <t>gi_v02_ab5587dd71eb</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -12195,26 +12195,26 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>In Muthukandiya, the skills required to build and maintain storage tanks were taught fairly easily and can be shared by the two trained masons, who are now finding work with other development agencies in the district.</t>
+          <t>Language is mankind's greatest invention – except, of course, that it was never invented.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>In Muthukandiya, 【the skills required to build and maintain storage tanks】 were taught fairly easily and can be shared by the two trained masons, who are now finding work with other development agencies in the district.</t>
+          <t>【Language】 is mankind's greatest invention – except, of course, that it was never invented.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
     </row>
-    <row r="59" ht="60" customHeight="1">
+    <row r="59" ht="44" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_850d6d7af56b</t>
+          <t>gi_v02_6b906789512f</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12229,26 +12229,26 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>The founder of the National Institute for Play, Stuart Brown, has described play as 'anything that spontaneously is done for its own sake'.</t>
+          <t>Half the world's 6,800 languages are likely to vanish within two generations—that's one language lost every ten days.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>【The founder of the National Institute for Play, Stuart Brown】, has described play as 'anything that spontaneously is done for its own sake'.</t>
+          <t>【Half the world's 6,800 languages】 are likely to vanish within two generations—that's one language lost every ten days.</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
-    <row r="60" ht="44" customHeight="1">
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="4" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_99ce32b92e45</t>
+          <t>gi_v02_c87cb35c0ed9</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -12263,26 +12263,26 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>This may be down to our brain's 'mirror neurons', which are known to mimic others' actions.</t>
+          <t>"All our rackets are sent from our manufacturer to Tampa, Florida, where our frames go through a . . . thorough customisation process."</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>【This】 may be down to our brain's 'mirror neurons', which are known to mimic others' actions.</t>
+          <t>"【All our rackets】 are sent from our manufacturer to Tampa, Florida, where our frames go through a . . . thorough customisation process."</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
-    <row r="61" ht="60" customHeight="1">
+    <row r="61" ht="44" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_795670181401</t>
+          <t>gi_v02_d8541971e30f</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -12297,13 +12297,13 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>A 9th-century stone cross from the Isle of Eigg shows, alongside the deer, boar and aurochs pursued by a mounted hunter, a speckled cat with tasselled ears.</t>
+          <t>Furthermore, the benefits associated with bilingual experience seem to start very early.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>【A 9th-century stone cross from the Isle of Eigg】 shows, alongside the deer, boar and aurochs pursued by a mounted hunter, a speckled cat with tasselled ears.</t>
+          <t>Furthermore, 【the benefits associated with bilingual experience】 seem to start very early.</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr"/>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_39018351fce4</t>
+          <t>gi_v02_ff77ec9c51dd</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>And, for those living near the equator in particular, its waxing and waning 【was】 more conspicuous than the passing of the seasons.</t>
+          <t>As an ecotourism-based resort most of the planning and development of the attraction has been concentrated on the need 【to co】-exist with the fragile natural environment of South Stradbroke Island to achieve sustainable development.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr"/>
@@ -12441,7 +12441,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_7d17af90cdb6</t>
+          <t>gi_v02_dcb2525113ac</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Silk 【was】 also 【used】 as diplomatic gifts by the emperor.</t>
+          <t>These efficiencies translated directly to the bottom line: the Eastgate's owners saved $3.5 million on a $36 million building because an air-conditioning plant 【didn't have】 to be imported.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr"/>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_5e0034c6decb</t>
+          <t>gi_v02_c1ea6e9b059b</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>But foresters have learned that forests need fires to clear out the brash and even to get seeds 【to germinate】.</t>
+          <t>The four-year pilot study included 380 families who were about to have their first child and who 【represented】 a cross-section of socio-economic status, age and family configurations.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_9b932be751a7</t>
+          <t>gi_v02_0391619f8cb8</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>EU research 【has】 now 【identified】 106 potential sites for tidal power, 80% round the coasts of Britain.</t>
+          <t>The GWR, aware that the new line would finally enable them to run trains into the heart of the City, 【invested】 almost £250,000 in the scheme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_5ef5d1a937c1</t>
+          <t>gi_v02_159595aa3eae</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Life based on DNA first appeared on Mars and then spread to Earth, where it then 【evolved】 into the myriad forms of plants and creatures that exist today.</t>
+          <t>This approach proved 【to be】 highly successful initially, with clear improvements in worker productivity in all facets of the business.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
@@ -12601,7 +12601,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4ad5fe1a3e44</t>
+          <t>gi_v02_e6fa42466149</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>There is a need 【to recognise】 the importance of access to credit for impoverished young people seeking to fulfil economic needs.</t>
+          <t>The cells are filled with air, which 【is】 why cork is so buoyant.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -12628,20 +12628,20 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr"/>
     </row>
-    <row r="8" ht="76" customHeight="1">
+    <row r="8" ht="92" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_f432653b3787</t>
+          <t>gi_v02_17be0efed583</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>At a banquet, a host 【would offer】 guests a plate with various spices piled upon it as a sign of the wealth at his or her disposal.</t>
+          <t>Ten years ago, a US commercial Iridium satellite smashed into an inactive Russian communications satellite called Cosmos-2251, creating thousands of new pieces of space shrapnel that now 【threaten】 other satellites in low Earth orbit – the zone stretching up to 2,000 kilometres in altitude.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d4a0b9f2d7ad</t>
+          <t>gi_v02_151cece17a52</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Its success 【is】 largely due to the fact that people with poor literacy skills can understand much of the information it contains about the non-timber forest products, thanks to its illustrations, anecdotes, stories and songs.</t>
+          <t>The aerosols 【could be delivered】 by artillery, high-flying aircraft or balloons.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_93e80893c204</t>
+          <t>gi_v02_7f56cff695e9</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>The so-called 'acey-deucy' stirrup placement, in which the rider's foot in his left stirrup is placed as much as 25 centimeters lower than the right, is believed to confer important speed advantages when 【turning】 on oval tracks.</t>
+          <t>It is this management mechanism that has allowed Alaska salmon stocks - and, accordingly, Alaska salmon fisheries - to prosper, even as salmon populations in the rest of the United States 【are】 increasingly 【considered】 threatened or even endangered.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c44dd81c1909</t>
+          <t>gi_v02_a7539c5deb2f</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>When it came to memorizing sequences of three-digit numbers, the difference between the memory contestant and the control subjects was, as 【expected】, immense.</t>
+          <t>Ants and other insects have structures in their brains called mushroom bodies, which 【are】 important for processing information, learning and memory.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_bba6ba5ed14d</t>
+          <t>gi_v02_6bd0e6afe04c</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>It is simply a common variant of human nature, one which iconoclasts 【do not let】 inhibit their reactions.</t>
+          <t>Southampton has been awarded £215,000 over three years 【to develop】 the turbines and is working with Marine Current Turbines, a subsidiary of IT Power, on the Lynmouth project.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_0794ff4e2390</t>
+          <t>gi_v02_c8107361df58</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>In the story of Little Red Riding Hood that European children 【are】 familiar with, a young girl on the way to see her grandmother meets a wolf and tells him where she is going.</t>
+          <t>As a rule, entire trees are not felled, but are pollarded so that they 【can regenerate】.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -12875,13 +12875,13 @@
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr"/>
     </row>
-    <row r="14" ht="76" customHeight="1">
+    <row r="14" ht="92" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_f80550ffcf24</t>
+          <t>gi_v02_81457fb3c020</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>When an irritant (such as a grain of sand) 【gets】 inside a certain type of oyster, mussel, or clam, the mollusc will secrete a fluid as a means of defence to coat the irritant.</t>
+          <t>Although male students 【tended】 to focus more on the practical aspects of work, such as "building a sound financial base", women, particularly those studying for humanities degrees, had a more idealistic outlook, saying making a contribution to society was a key career goal.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_bb22bb373874</t>
+          <t>gi_v02_a4cd7ded80bf</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>All that traffic 【can lead】 to disaster.</t>
+          <t>Social intelligence is the ability 【to understand】 and manage people in a business setting.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
@@ -12961,12 +12961,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_f638bc92e93b</t>
+          <t>gi_v02_ac66c809efd8</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>G-N04 分词短语</t>
+          <t>G-N01 区分谓语与非谓语</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>【Realising】 the importance of this breakthrough, he lost no time in patenting it.</t>
+          <t>This is yet another reason why Leonardo 【was aligned】 so closely with modern urban planning and centuries ahead of his time.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -12988,20 +12988,20 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
-    <row r="17" ht="92" customHeight="1">
+    <row r="17" ht="76" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_7fb8a3b2f818</t>
+          <t>gi_v02_2e95c89833ae</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Marie also gave lectures in Belgium, Brazil, Spain and Czechoslovakia and, in addition, had the satisfaction of seeing the development of the Curie Foundation in Paris, and the inauguration in 1932 in Warsaw of the Radium Institute, where her sister Bronia 【became】 director.</t>
+          <t>Goods from all over the world 【would come】 to the city through the port of Pozzuoli situated west of the bay of Naples in Italy and through the gigantic port of Ostia situated at the mouth of the Tiber River.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -13041,12 +13041,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_367ad4244ac9</t>
+          <t>gi_v02_dc13a1cee2a4</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>G-N01 区分谓语与非谓语</t>
+          <t>G-N04 分词短语</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>His scheme 【would employ】 up to 16 trillion minute spacecraft, each weighing about one gram, to form a transparent, sunlight-refracting sunshade in an orbit 1.5 million km above the Earth.</t>
+          <t>The breakthrough finally came when Nobel's company mixed liquid nitroglycerine with an inert absorbent silicate sand, 【known】 as 'diatomaceous earth'.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
@@ -13081,12 +13081,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c23fb6e90916</t>
+          <t>gi_v02_af56284cdda5</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>G-N01 区分谓语与非谓语</t>
+          <t>G-N04 分词短语</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>It was a visit that 【had】 a lasting impact on her life, and an immediate effect on her work.</t>
+          <t>Toward the end of the Middle Ages, the European middle classes began to desire the lifestyle of the elite, 【including】 their consumption of spices.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_4314f4077777</t>
+          <t>gi_v02_9784e8a15a51</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>In addition, a major collection like that of London's National Gallery is housed in numerous rooms, each with dozens of works, any one of which 【is】 likely to be worth more than all the average visitor possesses.</t>
+          <t>Such aids, while different, 【are】 still 【used】 even by the most educated in today's society due to their convenience.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_9a1038ccba03</t>
+          <t>gi_v02_6490642fdf4e</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Under pressure of rising academic standards, play is being replaced by test preparation in kindergartens and grade schools, and parents who 【aim】 to give their preschoolers a leg up are led to believe that flashcards and educational 'toys' are the path to success.</t>
+          <t>This pattern continued until she 【moved】 permanently to New Mexico in 1949.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_2b99ab199887</t>
+          <t>gi_v02_bf1728f50300</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Thunder, the shock wave that 【comes】 from a lightning flash, is thought to be the trigger for the torrential rain that is typical of storms.</t>
+          <t>But, in the face of aggressive tactics from the logging companies, they 【had】 no measure of the trees' financial worth.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -13228,7 +13228,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d79949acf94b</t>
+          <t>gi_v02_4987f97edd86</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>The device 【is aimed】 at a wide variety of users – from homeowners in the developing world who do not have a constant supply of water to people living off the grid in rural parts of the US.</t>
+          <t>Experience 【will show】 that to live in this way not only increases the life span but is also very healthy.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_ee6c5e8f3cd9</t>
+          <t>gi_v02_bcbd3118b92a</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Remarkably, she remained independent from shifting art trends and her work stayed true to her own vision, which 【was based】 on finding the essential, abstract forms in nature.</t>
+          <t>The existence in Paris at the Radium Institute of a stock of 1.5 grams of radium 【made】 a decisive contribution to the success of the experiments undertaken in the years around 1930.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_f639d4a86cb6</t>
+          <t>gi_v02_531bc791aeb5</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>The same 【happens】 with e-mails.</t>
+          <t>Having a stronger roof also 【makes】 it easier to grow a greater variety of plants, since the soil can be deeper.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_0811f8c0ace9</t>
+          <t>gi_v02_8175581ae6b8</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>The energy use and carbon emissions this 【generates】 is spectacular and largely unnecessary.</t>
+          <t>Our society 【has created】 a false dichotomy between play and learning.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c02645e48167</t>
+          <t>gi_v02_f7f2880cfde9</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>And a growing number of adventure tourism operators 【are trying】 to ensure that their activities benefit the local population and environment over the long term.</t>
+          <t>It was no good to eat, but they decided 【to run】 the stale wheat through rollers, just to see how it would turn out.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
@@ -13441,12 +13441,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_5455c30b03b2</t>
+          <t>gi_v02_9ce05f390689</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>G-N04 分词短语</t>
+          <t>G-N01 区分谓语与非谓语</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Many scholars think that the compact city, built upwards instead of outwards, 【integrated】 with nature (especially water systems), with efficient transport infrastructure, could help modern cities become more efficient and sustainable.</t>
+          <t>With luck, as the storm clouds 【gather】 this winter, laser-toting researchers could, for the first time, strike back.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4b0da9e4b63b</t>
+          <t>gi_v02_7e9c0225f113</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Controversy 【surrounds】 the practice of Reiki, some in opposition as they say that Reiki may offer only a perceived improvement in health and therefore only a 'placebo' effect.</t>
+          <t>The first commercial versions of the Desolenator are expected to be in operation in India early next year, after field tests 【are carried out】.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a61a5b99135c</t>
+          <t>gi_v02_33b030ab7045</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>These gondolas always weigh the same, whether or 【not】 they 【are carrying】 boats.</t>
+          <t>Many products fail because of a universal, but largely ignored, psychological bias: People irrationally 【overvalue】 benefits they currently possess relative to those they don't.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_db8d0b915a78</t>
+          <t>gi_v02_0fcbadba6cec</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>The increasing popularity of sea bathing during the late 1800s and early 1900s 【raised】 concerns about public safety and how to prevent people from drowning.</t>
+          <t>The stems that are left behind might then grow in size and develop more foliage and larger crowns or tops that 【produce】 more coverage for wildlife; they have a better chance to regenerate in a less crowded environment.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_93f4c297e2e7</t>
+          <t>gi_v02_d984488b526b</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>During the Empire, Rome 【was】 a huge city by ancient standards of about one million inhabitants.</t>
+          <t>Knowing what happens when people initially 【encounter】 misinformation holds tremendous importance for estimating the potential for subsequent problems.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e996bcbf2ad4</t>
+          <t>gi_v02_65c9138c9e82</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Carreiras 【explains】 that silbadores are able to pass a surprising amount of information via their whistles.</t>
+          <t>By Thursday March 6th it was running at full throttle, which 【was expected】 to be sustained for 60 hours.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_5b07b95cbaf2</t>
+          <t>gi_v02_e33a62bd66b2</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Streetcar's model 【works】 very similarly to those of its main rivals, Citycarclub and Whizzgo.</t>
+          <t>The provision of small loans to support the entrepreneurial dreams and ambitions of youth 【can be】 an effective means to help them change their lives.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_c5fdf5c505ba</t>
+          <t>gi_v02_4a245667adfe</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Therefore if the food is situated directly opposite from the sun, the bee will fly a straight run vertically downward; if it 【is】 in the same direction as the sun, it will fly directly upward from the colony nest.</t>
+          <t>It could take an hour and a half 【to travel】 8 km by horse-drawn carriage or bus.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -13748,25 +13748,25 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
     </row>
-    <row r="36" ht="76" customHeight="1">
+    <row r="36" ht="92" customHeight="1">
       <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_ce69bcff992d</t>
+          <t>gi_v02_9d212a928824</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>G-N01 区分谓语与非谓语</t>
+          <t>G-N04 分词短语</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Such chemical communication can be compared to the human use of visual and auditory channels (as in religious chants, advertising images and jingles, political slogans and martial music) 【to arouse】 and propagate moods and attitudes.</t>
+          <t>Meanwhile, AC's range and efficiency saw Westinghouse being given high prestige engineering projects, such as the Ames Hydro-electric Generating Plant (1891), and another one on Niagara Falls, 【culminating】 in the greatest public relations victory in 1893: the contract to illuminate the Columbian Exposition in Chicago.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5f8120975e2e</t>
+          <t>gi_v02_7f5d36550452</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>So heady were these first decades of cinema that America and Europe 【can be forgiven】 for assuming that they were the only game in town.</t>
+          <t>The great cathedrals and parish churches that 【lifted up】 their towers to heaven were not only acts of devotion in stone; they were also fiercely functional buildings.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_a673055a056d</t>
+          <t>gi_v02_6b13ad3530c0</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>G-N04 分词短语</t>
+          <t>G-N01 区分谓语与非谓语</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Between 1990 and 2012, the global land area 【devoted】 to growing oil palm trees grew from 6 to 17 million hectares, now accounting for around ten percent of total cropland in the entire world.</t>
+          <t>For those with high achievement needs, typically a minority in any organisation, the existence of external goals 【is】 less important because high achievers are already internally motivated.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -13868,25 +13868,25 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
     </row>
-    <row r="39" ht="76" customHeight="1">
+    <row r="39" ht="92" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_4aaacddf805b</t>
+          <t>gi_v02_3474ead07d56</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>G-N04 分词短语</t>
+          <t>G-N01 区分谓语与非谓语</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>The half-time schools 【established】 upon the Factory Act of 1833 allowed children to work and attend school.</t>
+          <t>Schatz studied the spontaneous speech of three-year-olds and found that these children used mental terms, and used them in circumstances where there 【was】 a contrast between, for example, not being sure where an object was located and finding it, or between pretending and reality.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_4ec243cd9f6c</t>
+          <t>gi_v02_c564a3155dce</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>In Indonesia, ecotourism started to become an important concept from 1995, in order to strengthen the domestic travelling movement, the local government 【targeting】 the right markets is a prerequisite for successful ecotourism.</t>
+          <t>The bank 【has given】 a cautious assessment that the region may have reached a turning point.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_d1ceb3d84b2a</t>
+          <t>gi_v02_34b421b71b8e</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>"The union was keen 【to discover】 whether it made more sense conserving the forest for subsistence use and the possible sale of fruit, game and medicinal plants, than selling trees for timber," says Shanley.</t>
+          <t>However, there are multiple reasons why conservationists 【cite】 the rapid spread of oil palm plantations as a major concern.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -13988,20 +13988,20 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
     </row>
-    <row r="42" ht="92" customHeight="1">
+    <row r="42" ht="76" customHeight="1">
       <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_5341eecf2c1c</t>
+          <t>gi_v02_5d4dcd6e55dc</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>The basic premise 【involves】 using cloning technology to turn the DNA of extinct animals into a fertilised embryo, which is carried by the nearest relative still in existence -- in this case, the abundant band-tailed pigeon -- before being born as a living, breathing animal.</t>
+          <t>And while this 【may not sound】 like anything worth losing sleep over, the international press would have us believe that the consequences could be devastating.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr"/>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_23a54c7c13fb</t>
+          <t>gi_v02_06b22134544b</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>It also 【found】 that 13 per cent of boys and 10 per cent of girls were overweight.</t>
+          <t>Just the knowledge that one has control 【is】 sufficient.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_056c7e079651</t>
+          <t>gi_v02_84b5297ddcaf</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>It was Pasteur's 'germ theory' that gave bacteria the poor image that 【endures】 today.</t>
+          <t>Such games indirectly 【teach】 children about aspects of life on earth.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_8c6504dae1af</t>
+          <t>gi_v02_c4fc0857d904</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>A new generation of seedlings have been bred and tested 【to see】 if they can withstand the fungus by cutting a small slit in the bark and injecting a tiny amount of the pathogen.</t>
+          <t>Passenger pigeons are one of the pioneering species in this field, but they are far from the only ones on which this cutting-edge technology 【is being trialled】.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr"/>
@@ -14161,12 +14161,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_eee68f140387</t>
+          <t>gi_v02_4122bf2c62d4</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>G-N01 区分谓语与非谓语</t>
+          <t>G-N04 分词短语</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>For instance, 【knowing】 more than one language can cause speakers to name pictures more slowly, and can increase 'tip-of-the-tongue states', when you can almost, but not quite, bring a word to mind.</t>
+          <t>Perkin originally named his dye Tyrian Purple, but it later became commonly known as mauve (from the French for the plant 【used】 to make the colour violet).</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_3df26a449e4c</t>
+          <t>gi_v02_8039d2e2fcdb</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>The artificial sweetener, saccharin, 【was】 the unintentional result of a medical scientist's work on a chemical treatment for gastric ulcers.</t>
+          <t>Their story, though not as spectacular to the eye, 【will】 surely 【turn out】 to be as subtle and as complex.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_04bd11d0072a</t>
+          <t>gi_v02_f9ed39a26fe4</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>It【's going】 to have more to do with productivity.</t>
+          <t>Yong's book is in many ways a plea for microbial tolerance, pointing out that while fewer than one hundred species of bacteria 【bring】 disease, many thousands more play a vital role in maintaining our health.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
@@ -14281,7 +14281,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_647c9fe503b1</t>
+          <t>gi_v02_d41b168afdc7</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>However, Pearson and his partners 【persisted】.</t>
+          <t>'If we【're putting】 elm back into the landscape, a small element of it is not native – are we bothered about that?'</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
@@ -14321,7 +14321,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_8039d2e2fcdb</t>
+          <t>gi_v02_70090aa5fd57</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Their story, though not as spectacular to the eye, 【will】 surely 【turn out】 to be as subtle and as complex.</t>
+          <t>The resin was allowed to cool in shallow trays until it 【hardened】, and then broken up and ground into powder.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
@@ -14361,12 +14361,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_5db8594c6a93</t>
+          <t>gi_v02_a04e38db3d8f</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>G-N01 区分谓语与非谓语</t>
+          <t>G-N04 分词短语</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>This 【gets separated】 into cocoa solids and fat called cocoa butter.</t>
+          <t>Usually they come out of a chaotic, haphazard mess, which is why big companies, full of managers schooled in business programmes 【designed】 to eliminate random variation and mistakes, struggle with them.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_070008510acc</t>
+          <t>gi_v02_fb854c32faac</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Removing invasive plants 【might be】 another primary goal of a TSI Cut.</t>
+          <t>In more northern climes, however, where seasonal agriculture 【was practised】, the solar year became more crucial.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
@@ -14441,12 +14441,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e6fa42466149</t>
+          <t>gi_v02_dd8c77be2a68</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>G-N01 区分谓语与非谓语</t>
+          <t>G-N04 分词短语</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>The cells are filled with air, which 【is】 why cork is so buoyant.</t>
+          <t>The kākāpō, also 【known】 as the owl parrot, is a large, forest-dwelling bird, with a pale owl-like face.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_32c683381673</t>
+          <t>gi_v02_1ee4d928b763</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Probably all of us could make a sale if the product was something we truly believed in, but professional salespeople 【are】 in a different league—the best of them can always sell different items to suitable customers in the best time.</t>
+          <t>The study team 【used】 neuroimaging equipment to contrast the brain activity of silbadores while listening to whistled and spoken Spanish.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -14508,25 +14508,25 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>从句里的谓语</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
     </row>
-    <row r="55" ht="92" customHeight="1">
+    <row r="55" ht="76" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_e9bf9e1561b4</t>
+          <t>gi_v02_e3ae7e1f8ac4</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>G-N04 分词短语</t>
+          <t>G-N01 区分谓语与非谓语</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Research with creative scientists by Simonton (1988) brought him to the conclusion that above a certain high level, characteristics such as independence seemed to contribute more to reaching the highest levels of expertise than intellectual skills, due to the great demands of effort and time 【needed】 for learning and practice.</t>
+          <t>Chocolate 【is】 especially popular in Europe and the United States.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_e7555c84d200</t>
+          <t>gi_v02_93e80893c204</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>If the individual knows that he or she can control the noise, this 【seems】 to eliminate both its negative effects at the time and its after-effects.</t>
+          <t>The so-called 'acey-deucy' stirrup placement, in which the rider's foot in his left stirrup is placed as much as 25 centimeters lower than the right, is believed to confer important speed advantages when 【turning】 on oval tracks.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>从句里的谓语</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr"/>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_0fd7725761e4</t>
+          <t>gi_v02_73acc47284ff</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Westinghouse countered by hiring the best lawyers of the day 【to defend】 the prisoner in question, as well as to prevent the system of execution.</t>
+          <t>First, the programme 【began】 too late.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>非谓语（不定式、分词、动名词）</t>
+          <t>主句谓语</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr"/>
@@ -14641,7 +14641,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_b1d47f7c4989</t>
+          <t>gi_v02_2b7d3f347014</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Scientists first recognized the value of the practice more than 60 years ago, when they 【found】 that rats fed a low-calorie diet lived longer on average than free-feeding rats and also had a reduced incidence of conditions that become increasingly common in old age.</t>
+          <t>Some plants reach maximal photosynthesis at one-quarter full sunlight, and others, like sugarcane, never reach a maximum, but continue to increase photosynthesis rate as light intensity 【rises】.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_21200fb366dc</t>
+          <t>gi_v02_05ff65a439ce</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Being able to keep enough water at roof height and distribute it right across the rooftop is crucial to maintaining the plants on any green roof – especially on 'edible roofs' where fruit and vegetables 【are farmed】.</t>
+          <t>Perhaps it is a bizarre coincidence, yet MasterCard's findings 【fit】 quite neatly with two important issues in Asia: economic leadership and debt.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -14715,18 +14715,18 @@
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
     </row>
-    <row r="60" ht="76" customHeight="1">
+    <row r="60" ht="92" customHeight="1">
       <c r="A60" s="4" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>gi_v02_082a9179fa85</t>
+          <t>gi_v02_e9bf9e1561b4</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>G-N01 区分谓语与非谓语</t>
+          <t>G-N04 分词短语</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>The original patent 【outlined】 a three-stage process, in which phenol and formaldehyde (from wood or coal) were initially combined under vacuum inside a large egg-shaped kettle.</t>
+          <t>Research with creative scientists by Simonton (1988) brought him to the conclusion that above a certain high level, characteristics such as independence seemed to contribute more to reaching the highest levels of expertise than intellectual skills, due to the great demands of effort and time 【needed】 for learning and practice.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -14748,20 +14748,20 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>主句谓语</t>
+          <t>非谓语（不定式、分词、动名词）</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
     </row>
-    <row r="61" ht="92" customHeight="1">
+    <row r="61" ht="76" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>gi_v02_7f8577e8b54f</t>
+          <t>gi_v02_4314f4077777</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>The simultaneous production of masses of bamboo seeds (in some cases lying 12 to 15 centimetres deep on the ground) is more than all the seed-eating animals can cope with at the time, so that some seeds 【escape】 being eaten and grow up to form the next generation (Evans 1976).</t>
+          <t>In addition, a major collection like that of London's National Gallery is housed in numerous rooms, each with dozens of works, any one of which 【is】 likely to be worth more than all the average visitor possesses.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
